--- a/data-recover/Databaze_rustu_DD-test.xlsx
+++ b/data-recover/Databaze_rustu_DD-test.xlsx
@@ -5,24 +5,37 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rene.filipi\Git\RodGrowth_database\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rene.filipi\Git\RodGrowth_database\data-recover\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9ED22D7A-082E-4C56-9396-56DD8B7B5B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{623F9EDD-D53E-48E2-8D9A-014BD7BAC406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22932" yWindow="-5460" windowWidth="30936" windowHeight="16776" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-16320" yWindow="-12615" windowWidth="16440" windowHeight="28320" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Graf1" sheetId="1" r:id="rId1"/>
     <sheet name="RustDD_Data" sheetId="2" r:id="rId2"/>
     <sheet name="DD_key" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="22">
   <si>
     <t>Kampan</t>
   </si>
@@ -72,9 +85,6 @@
     <t>XX02</t>
   </si>
   <si>
-    <t>XX03</t>
-  </si>
-  <si>
     <t>DD_No</t>
   </si>
   <si>
@@ -84,7 +94,13 @@
     <t>OUR/TOP</t>
   </si>
   <si>
-    <t>XX01_naklon</t>
+    <t>XX02_naklon</t>
+  </si>
+  <si>
+    <t>DR03</t>
+  </si>
+  <si>
+    <t>UXCX3</t>
   </si>
 </sst>
 </file>
@@ -94,7 +110,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -107,6 +123,13 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <charset val="238"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="238"/>
@@ -133,7 +156,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -152,10 +175,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
@@ -456,169 +481,367 @@
                   <c:v>29.7</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>29.85</c:v>
+                  <c:v>29.9</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>29.96</c:v>
+                  <c:v>29.9</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>30.07</c:v>
+                  <c:v>29.9</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>30.18</c:v>
+                  <c:v>29.9</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>30.29</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>30.4</c:v>
+                  <c:v>30</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>30.51</c:v>
+                  <c:v>30.1</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>30.62</c:v>
+                  <c:v>30.1</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>30.73</c:v>
+                  <c:v>30.1</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>30.84</c:v>
+                  <c:v>30.1</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>30.95</c:v>
+                  <c:v>30.2</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>31.06</c:v>
+                  <c:v>30.2</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>31.17</c:v>
+                  <c:v>30.5</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>31.28</c:v>
+                  <c:v>30.5</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>31.39</c:v>
+                  <c:v>30.7</c:v>
                 </c:pt>
                 <c:pt idx="92">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>31.4</c:v>
+                </c:pt>
+                <c:pt idx="100">
                   <c:v>31.5</c:v>
                 </c:pt>
-                <c:pt idx="93">
-                  <c:v>31.61</c:v>
-                </c:pt>
-                <c:pt idx="94">
-                  <c:v>31.72</c:v>
-                </c:pt>
-                <c:pt idx="95">
-                  <c:v>31.83</c:v>
-                </c:pt>
-                <c:pt idx="96">
-                  <c:v>31.94</c:v>
-                </c:pt>
-                <c:pt idx="97">
-                  <c:v>32.049999999999997</c:v>
-                </c:pt>
-                <c:pt idx="98">
-                  <c:v>32.159999999999997</c:v>
-                </c:pt>
-                <c:pt idx="99">
-                  <c:v>32.270000000000003</c:v>
-                </c:pt>
-                <c:pt idx="100">
-                  <c:v>32.380000000000003</c:v>
-                </c:pt>
                 <c:pt idx="101">
-                  <c:v>32.49</c:v>
+                  <c:v>31.5</c:v>
                 </c:pt>
                 <c:pt idx="102">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>32.1</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="122">
                   <c:v>32.6</c:v>
                 </c:pt>
-                <c:pt idx="103">
-                  <c:v>32.71</c:v>
-                </c:pt>
-                <c:pt idx="104">
-                  <c:v>32.82</c:v>
-                </c:pt>
-                <c:pt idx="105">
-                  <c:v>32.93</c:v>
-                </c:pt>
-                <c:pt idx="106">
-                  <c:v>33.04</c:v>
-                </c:pt>
-                <c:pt idx="107">
-                  <c:v>33.15</c:v>
-                </c:pt>
-                <c:pt idx="108">
-                  <c:v>33.26</c:v>
-                </c:pt>
-                <c:pt idx="109">
-                  <c:v>33.369999999999997</c:v>
-                </c:pt>
-                <c:pt idx="110">
-                  <c:v>33.479999999999997</c:v>
-                </c:pt>
-                <c:pt idx="111">
-                  <c:v>33.590000000000003</c:v>
-                </c:pt>
-                <c:pt idx="112">
-                  <c:v>33.700000000000003</c:v>
-                </c:pt>
-                <c:pt idx="113">
-                  <c:v>33.81</c:v>
-                </c:pt>
-                <c:pt idx="114">
-                  <c:v>33.92</c:v>
-                </c:pt>
-                <c:pt idx="115">
-                  <c:v>34.03</c:v>
-                </c:pt>
-                <c:pt idx="116">
-                  <c:v>34.14</c:v>
-                </c:pt>
-                <c:pt idx="117">
-                  <c:v>34.25</c:v>
-                </c:pt>
-                <c:pt idx="118">
-                  <c:v>34.36</c:v>
-                </c:pt>
-                <c:pt idx="119">
-                  <c:v>34.47</c:v>
-                </c:pt>
-                <c:pt idx="120">
-                  <c:v>34.58</c:v>
-                </c:pt>
-                <c:pt idx="121">
-                  <c:v>22.4</c:v>
-                </c:pt>
-                <c:pt idx="122">
-                  <c:v>22.4</c:v>
-                </c:pt>
                 <c:pt idx="123">
-                  <c:v>22.6</c:v>
+                  <c:v>32.6</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>22.6</c:v>
+                  <c:v>32.6</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>22.7</c:v>
+                  <c:v>32.700000000000003</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>22.7</c:v>
+                  <c:v>32.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>22.8</c:v>
+                  <c:v>32.799999999999997</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>22.8</c:v>
+                  <c:v>32.9</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>22.8</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>23</c:v>
+                  <c:v>33</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>23</c:v>
+                  <c:v>33.9</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>28.5</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>28.7</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>28.8</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>29</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>29.2</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>29.4</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>29.5</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>29.7</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>29.7</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>29.9</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>30</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>30.1</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>30.1</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>30.1</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>30.1</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>30.2</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>30.2</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>30.7</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>30.9</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>31.2</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>31.3</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>31.4</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>31.5</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>31.6</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>31.8</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>31.9</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>32.1</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>32.4</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>32.6</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>32.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>32.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>32.9</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>33</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>33.9</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -639,22 +862,22 @@
                   <c:v>9.7884615384615383</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10.42307692307692</c:v>
+                  <c:v>10.423076923076923</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10.42307692307692</c:v>
+                  <c:v>10.423076923076923</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>8.5192307692307701</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>10.21153846153846</c:v>
+                  <c:v>10.211538461538462</c:v>
                 </c:pt>
                 <c:pt idx="7">
                   <c:v>8.5192307692307701</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>10.63461538461539</c:v>
+                  <c:v>10.634615384615385</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>9.365384615384615</c:v>
@@ -663,121 +886,121 @@
                   <c:v>9.365384615384615</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>11.05769230769231</c:v>
+                  <c:v>11.057692307692308</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>10.63461538461539</c:v>
+                  <c:v>10.634615384615385</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>11.90384615384615</c:v>
+                  <c:v>11.903846153846153</c:v>
                 </c:pt>
                 <c:pt idx="14">
                   <c:v>11.26923076923077</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>12.32692307692308</c:v>
+                  <c:v>12.326923076923077</c:v>
                 </c:pt>
                 <c:pt idx="16">
                   <c:v>10</c:v>
                 </c:pt>
                 <c:pt idx="17">
-                  <c:v>10.42307692307692</c:v>
+                  <c:v>10.423076923076923</c:v>
                 </c:pt>
                 <c:pt idx="18">
                   <c:v>11.48076923076923</c:v>
                 </c:pt>
                 <c:pt idx="19">
-                  <c:v>12.11538461538462</c:v>
+                  <c:v>12.115384615384617</c:v>
                 </c:pt>
                 <c:pt idx="20">
-                  <c:v>11.05769230769231</c:v>
+                  <c:v>11.057692307692308</c:v>
                 </c:pt>
                 <c:pt idx="21">
-                  <c:v>12.32692307692308</c:v>
+                  <c:v>12.326923076923077</c:v>
                 </c:pt>
                 <c:pt idx="22">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="23">
-                  <c:v>12.32692307692308</c:v>
+                  <c:v>12.326923076923077</c:v>
                 </c:pt>
                 <c:pt idx="24">
                   <c:v>12.75</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>11.69230769230769</c:v>
+                  <c:v>11.692307692307693</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>12.11538461538462</c:v>
+                  <c:v>12.115384615384617</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>13.17307692307692</c:v>
+                  <c:v>13.173076923076923</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>12.96153846153846</c:v>
+                  <c:v>12.961538461538462</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>13.38461538461539</c:v>
+                  <c:v>13.384615384615385</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>13.976923076923081</c:v>
+                  <c:v>13.976923076923077</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>13.59615384615385</c:v>
+                  <c:v>13.596153846153847</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>13.59615384615385</c:v>
+                  <c:v>13.596153846153847</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>12.45384615384615</c:v>
+                  <c:v>12.453846153846154</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="36">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="37">
                   <c:v>12.75</c:v>
                 </c:pt>
                 <c:pt idx="38">
-                  <c:v>13.04615384615385</c:v>
+                  <c:v>13.046153846153846</c:v>
                 </c:pt>
                 <c:pt idx="39">
-                  <c:v>13.17307692307692</c:v>
+                  <c:v>13.173076923076923</c:v>
                 </c:pt>
                 <c:pt idx="40">
                   <c:v>13.63846153846154</c:v>
                 </c:pt>
                 <c:pt idx="41">
-                  <c:v>12.96153846153846</c:v>
+                  <c:v>12.961538461538462</c:v>
                 </c:pt>
                 <c:pt idx="42">
-                  <c:v>13.80769230769231</c:v>
+                  <c:v>13.807692307692308</c:v>
                 </c:pt>
                 <c:pt idx="43">
-                  <c:v>14.61153846153846</c:v>
+                  <c:v>14.611538461538462</c:v>
                 </c:pt>
                 <c:pt idx="44">
                   <c:v>12.75</c:v>
                 </c:pt>
                 <c:pt idx="45">
-                  <c:v>13.723076923076921</c:v>
+                  <c:v>13.723076923076924</c:v>
                 </c:pt>
                 <c:pt idx="46">
-                  <c:v>15.542307692307689</c:v>
+                  <c:v>15.542307692307693</c:v>
                 </c:pt>
                 <c:pt idx="47">
-                  <c:v>13.892307692307689</c:v>
+                  <c:v>13.892307692307693</c:v>
                 </c:pt>
                 <c:pt idx="48">
-                  <c:v>12.32692307692308</c:v>
+                  <c:v>12.326923076923077</c:v>
                 </c:pt>
                 <c:pt idx="49">
-                  <c:v>13.06730769230769</c:v>
+                  <c:v>13.067307692307693</c:v>
                 </c:pt>
                 <c:pt idx="50">
                   <c:v>12.64423076923077</c:v>
@@ -786,67 +1009,67 @@
                   <c:v>14.125</c:v>
                 </c:pt>
                 <c:pt idx="52">
-                  <c:v>12.96153846153846</c:v>
+                  <c:v>12.961538461538462</c:v>
                 </c:pt>
                 <c:pt idx="53">
-                  <c:v>13.17307692307692</c:v>
+                  <c:v>13.173076923076923</c:v>
                 </c:pt>
                 <c:pt idx="54">
                   <c:v>15.28846153846154</c:v>
                 </c:pt>
                 <c:pt idx="55">
-                  <c:v>13.06730769230769</c:v>
+                  <c:v>13.067307692307693</c:v>
                 </c:pt>
                 <c:pt idx="56">
-                  <c:v>12.96153846153846</c:v>
+                  <c:v>12.961538461538462</c:v>
                 </c:pt>
                 <c:pt idx="57">
-                  <c:v>13.27884615384615</c:v>
+                  <c:v>13.278846153846153</c:v>
                 </c:pt>
                 <c:pt idx="58">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="59">
-                  <c:v>12.32692307692308</c:v>
+                  <c:v>12.326923076923077</c:v>
                 </c:pt>
                 <c:pt idx="60">
-                  <c:v>12.53846153846154</c:v>
+                  <c:v>12.538461538461538</c:v>
                 </c:pt>
                 <c:pt idx="61">
-                  <c:v>13.80769230769231</c:v>
+                  <c:v>13.807692307692308</c:v>
                 </c:pt>
                 <c:pt idx="62">
-                  <c:v>13.59615384615385</c:v>
+                  <c:v>13.596153846153847</c:v>
                 </c:pt>
                 <c:pt idx="63">
-                  <c:v>13.59615384615385</c:v>
+                  <c:v>13.596153846153847</c:v>
                 </c:pt>
                 <c:pt idx="64">
-                  <c:v>14.23076923076923</c:v>
+                  <c:v>14.230769230769232</c:v>
                 </c:pt>
                 <c:pt idx="65">
-                  <c:v>14.23076923076923</c:v>
+                  <c:v>14.230769230769232</c:v>
                 </c:pt>
                 <c:pt idx="66">
-                  <c:v>11.265384615384621</c:v>
+                  <c:v>11.265384615384615</c:v>
                 </c:pt>
                 <c:pt idx="67">
-                  <c:v>14.015384615384621</c:v>
+                  <c:v>14.015384615384615</c:v>
                 </c:pt>
                 <c:pt idx="68">
-                  <c:v>12.32307692307692</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="69">
-                  <c:v>13.38076923076923</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="70">
-                  <c:v>13.38076923076923</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="71">
-                  <c:v>12.746153846153851</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="72">
-                  <c:v>13.38076923076923</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="73">
                   <c:v>11.9</c:v>
@@ -855,175 +1078,373 @@
                   <c:v>13.16923076923077</c:v>
                 </c:pt>
                 <c:pt idx="75">
-                  <c:v>13.38076923076923</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="76">
-                  <c:v>12.957692307692311</c:v>
+                  <c:v>12.957692307692309</c:v>
                 </c:pt>
                 <c:pt idx="77">
-                  <c:v>13.0634615384615</c:v>
+                  <c:v>13.592307692307692</c:v>
                 </c:pt>
                 <c:pt idx="78">
-                  <c:v>13.0846153846154</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="79">
-                  <c:v>13.1057692307692</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="80">
-                  <c:v>13.1269230769231</c:v>
+                  <c:v>13.803846153846155</c:v>
                 </c:pt>
                 <c:pt idx="81">
-                  <c:v>13.1480769230769</c:v>
+                  <c:v>13.592307692307692</c:v>
                 </c:pt>
                 <c:pt idx="82">
-                  <c:v>13.169230769230801</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="83">
-                  <c:v>13.1903846153846</c:v>
+                  <c:v>13.803846153846155</c:v>
                 </c:pt>
                 <c:pt idx="84">
-                  <c:v>13.211538461538501</c:v>
+                  <c:v>14.226923076923077</c:v>
                 </c:pt>
                 <c:pt idx="85">
-                  <c:v>13.2326923076923</c:v>
+                  <c:v>13.16923076923077</c:v>
                 </c:pt>
                 <c:pt idx="86">
-                  <c:v>13.253846153846199</c:v>
+                  <c:v>14.226923076923077</c:v>
                 </c:pt>
                 <c:pt idx="87">
-                  <c:v>13.275</c:v>
+                  <c:v>11.9</c:v>
                 </c:pt>
                 <c:pt idx="88">
-                  <c:v>13.296153846154001</c:v>
+                  <c:v>13.126923076923077</c:v>
                 </c:pt>
                 <c:pt idx="89">
-                  <c:v>13.317307692307899</c:v>
+                  <c:v>11.9</c:v>
                 </c:pt>
                 <c:pt idx="90">
-                  <c:v>13.3384615384618</c:v>
+                  <c:v>13.592307692307692</c:v>
                 </c:pt>
                 <c:pt idx="91">
-                  <c:v>13.359615384615701</c:v>
+                  <c:v>11.688461538461539</c:v>
                 </c:pt>
                 <c:pt idx="92">
-                  <c:v>13.3807692307696</c:v>
+                  <c:v>13.507692307692309</c:v>
                 </c:pt>
                 <c:pt idx="93">
-                  <c:v>13.4019230769235</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="94">
-                  <c:v>13.423076923077399</c:v>
+                  <c:v>12.111538461538462</c:v>
                 </c:pt>
                 <c:pt idx="95">
-                  <c:v>13.4442307692313</c:v>
+                  <c:v>13.042307692307693</c:v>
                 </c:pt>
                 <c:pt idx="96">
-                  <c:v>13.465384615385201</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="97">
-                  <c:v>13.4865384615391</c:v>
+                  <c:v>11.688461538461539</c:v>
                 </c:pt>
                 <c:pt idx="98">
-                  <c:v>13.507692307693</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="99">
-                  <c:v>13.528846153846899</c:v>
+                  <c:v>14.226923076923077</c:v>
                 </c:pt>
                 <c:pt idx="100">
-                  <c:v>13.5500000000008</c:v>
+                  <c:v>13.16923076923077</c:v>
                 </c:pt>
                 <c:pt idx="101">
-                  <c:v>13.571153846154701</c:v>
+                  <c:v>11.9</c:v>
                 </c:pt>
                 <c:pt idx="102">
-                  <c:v>13.5923076923086</c:v>
+                  <c:v>11.9</c:v>
                 </c:pt>
                 <c:pt idx="103">
-                  <c:v>13.6134615384625</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="104">
-                  <c:v>13.634615384616399</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="105">
-                  <c:v>13.6557692307703</c:v>
+                  <c:v>11.9</c:v>
                 </c:pt>
                 <c:pt idx="106">
-                  <c:v>13.676923076924201</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="107">
-                  <c:v>13.6980769230781</c:v>
+                  <c:v>14.057692307692308</c:v>
                 </c:pt>
                 <c:pt idx="108">
-                  <c:v>13.719230769232</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="109">
-                  <c:v>13.740384615385899</c:v>
+                  <c:v>13.803846153846155</c:v>
                 </c:pt>
                 <c:pt idx="110">
-                  <c:v>13.7615384615398</c:v>
+                  <c:v>13.423076923076923</c:v>
                 </c:pt>
                 <c:pt idx="111">
-                  <c:v>13.782692307693701</c:v>
+                  <c:v>12.196153846153846</c:v>
                 </c:pt>
                 <c:pt idx="112">
-                  <c:v>13.8038461538476</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="113">
-                  <c:v>13.8250000000015</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="114">
-                  <c:v>13.846153846155399</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="115">
-                  <c:v>13.8673076923093</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="116">
-                  <c:v>13.888461538463201</c:v>
+                  <c:v>13.16923076923077</c:v>
                 </c:pt>
                 <c:pt idx="117">
-                  <c:v>13.9096153846171</c:v>
+                  <c:v>12.873076923076924</c:v>
                 </c:pt>
                 <c:pt idx="118">
-                  <c:v>13.930769230771</c:v>
+                  <c:v>14.184615384615386</c:v>
                 </c:pt>
                 <c:pt idx="119">
-                  <c:v>13.951923076924899</c:v>
+                  <c:v>11.688461538461539</c:v>
                 </c:pt>
                 <c:pt idx="120">
-                  <c:v>13.9730769230788</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="121">
-                  <c:v>8.7307692307692299</c:v>
+                  <c:v>11.053846153846154</c:v>
                 </c:pt>
                 <c:pt idx="122">
-                  <c:v>9.1538461538461533</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="123">
-                  <c:v>9.7884615384615383</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="124">
-                  <c:v>10.42307692307692</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="125">
-                  <c:v>10.42307692307692</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="126">
-                  <c:v>8.5192307692307701</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="127">
-                  <c:v>10.21153846153846</c:v>
+                  <c:v>12.746153846153847</c:v>
                 </c:pt>
                 <c:pt idx="128">
-                  <c:v>8.5192307692307701</c:v>
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
                 <c:pt idx="129">
-                  <c:v>10.63461538461539</c:v>
+                  <c:v>13.380769230769232</c:v>
                 </c:pt>
                 <c:pt idx="130">
-                  <c:v>9.365384615384615</c:v>
+                  <c:v>12.534615384615385</c:v>
                 </c:pt>
                 <c:pt idx="131">
-                  <c:v>9.365384615384615</c:v>
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>11.265384615384615</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>14.015384615384615</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>13.16923076923077</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>12.957692307692309</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>13.592307692307692</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>13.803846153846155</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>13.592307692307692</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>13.803846153846155</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>14.226923076923077</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>13.16923076923077</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>14.226923076923077</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>13.126923076923077</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>13.592307692307692</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>11.688461538461539</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>13.507692307692309</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>12.111538461538462</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>13.042307692307693</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>11.688461538461539</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>14.226923076923077</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>13.16923076923077</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>11.9</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>14.057692307692308</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>13.803846153846155</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>13.423076923076923</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>12.196153846153846</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>13.16923076923077</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>12.873076923076924</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>14.184615384615386</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>11.688461538461539</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>11.053846153846154</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>12.746153846153847</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>12.323076923076924</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>13.380769230769232</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>12.534615384615385</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>12.323076923076924</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1031,7 +1452,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-17AD-43FB-B175-80002D7D80F2}"/>
+              <c16:uniqueId val="{00000000-A97C-4640-A5FF-9FC1A856957F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1071,6 +1492,384 @@
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="192"/>
+                <c:pt idx="0">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>36</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>36.5</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>37</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>37.1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>37.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>37.200000000000003</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>37.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>37.4</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>37.4</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>37.4</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>37.6</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>37.6</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>37.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>37.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>37.9</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>38</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>38.1</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>38.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>38.4</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>38.4</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>38.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>38.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>38.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>38.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>38.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>38.9</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>38.9</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>39</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>39.1</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>39.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>39.4</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>39.5</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>39.6</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>39.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>39.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>39.9</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>40</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>40.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>40.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>40.299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>40.4</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>40.5</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>40.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>40.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>40.700000000000003</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>40.799999999999997</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>40.9</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>41</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>41.1</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>41.2</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>41.3</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>41.4</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>41.5</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>41.6</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>41.7</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>41.8</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>41.9</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>42.1</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>42.2</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>42.3</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>42.4</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>42.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:xVal>
@@ -1080,13 +1879,391 @@
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="192"/>
+                <c:pt idx="0">
+                  <c:v>13.467199999999998</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>10.414900000000005</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>13.236699999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>11.889699999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>12.406099999999995</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>13.480300000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>13.480300000000002</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>12.102974999999995</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>11.593899999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>9.733700000000006</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>11.777449999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>11.777449999999998</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>12.417274999999997</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>12.497800000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>9.8384999999999998</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>12.746699999999999</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>10.946800000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>11.306000000000001</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>11.947599999999996</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>11.410500000000001</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>11.609074999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>12.445399999999998</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>12.406100000000002</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>12.406100000000002</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>9.8123000000000005</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>11.822349999999997</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>11.249874999999999</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>12.361149999999997</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>11.957050000000001</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>11.788675000000001</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>10.179100000000004</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>13.362400000000004</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>9.8909000000000038</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>13.910199999999998</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>13.910199999999998</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>9.9957000000000065</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>12.720349999999996</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>9.4454999999999991</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>10.336300000000001</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>12.798925000000001</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>12.136649999999998</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>12.327500000000001</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>11.0175</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>11.842800000000002</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>11.842800000000002</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>10.8734</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>12.226449999999998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>11.0175</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>12.361149999999997</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>12.4285</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>13.057099999999997</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>12.518300000000002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>13.519600000000002</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>12.943199999999999</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>12.943199999999999</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>9.471700000000002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>11.575399999999998</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>13.685699999999999</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>13.685699999999999</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>14.089799999999999</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.372375</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>8.9870000000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>12.226449999999998</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>12.226449999999998</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>13.270699999999998</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>12.035625</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>10.703100000000003</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>10.349399999999997</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>13.348949999999999</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>13.348949999999999</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>12.497800000000002</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>10.7555</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>10.336300000000001</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>11.109199999999998</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>10.388699999999998</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>10.454200000000002</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>13.898975</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>11.724900000000005</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>11.214</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>10.545899999999996</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>10.899600000000003</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>10.467300000000002</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>10.428000000000001</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>10.113600000000003</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>12.271349999999996</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>12.930100000000003</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>10.663800000000002</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>11.200900000000001</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>12.248899999999997</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>13.977550000000001</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>12.147874999999999</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>11.620099999999995</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>13.595899999999997</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>12.078599999999996</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>11.945824999999999</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>12.608099999999997</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>13.988774999999997</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>12.305024999999997</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>13.113224999999996</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>14.29185</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>11.384300000000001</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>11.790399999999996</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>12.125425000000002</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>10.856999999999999</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>11.272324999999999</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>11.799899999999997</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>15.201074999999999</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>12.524000000000001</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>11.436699999999998</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>12.630550000000001</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>12.4285</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>12.147874999999999</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>13.472424999999998</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>11.519274999999997</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>13.225474999999996</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>12.989750000000001</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>13.315274999999998</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>11.957050000000001</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>12.944849999999995</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>12.551974999999995</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>13.135675000000001</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>12.922399999999998</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>12.31625</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>12.507074999999999</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:yVal>
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-17AD-43FB-B175-80002D7D80F2}"/>
+              <c16:uniqueId val="{00000001-A97C-4640-A5FF-9FC1A856957F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1755,17 +2932,15 @@
         <v>8</v>
       </c>
       <c r="D2" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E2" s="4">
         <v>8.7307692307692299</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="7">
         <v>22.4</v>
       </c>
-      <c r="G2" s="8">
-        <v>1</v>
-      </c>
+      <c r="G2" s="10"/>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
@@ -1775,15 +2950,15 @@
         <v>8</v>
       </c>
       <c r="D3" s="7">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E3" s="4">
         <v>9.1538461538461533</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="7">
         <v>22.4</v>
       </c>
-      <c r="G3" s="9"/>
+      <c r="G3" s="11"/>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
@@ -1793,15 +2968,15 @@
         <v>8</v>
       </c>
       <c r="D4" s="7">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4">
         <v>9.7884615384615383</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="7">
         <v>22.6</v>
       </c>
-      <c r="G4" s="9"/>
+      <c r="G4" s="11"/>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -1811,15 +2986,15 @@
         <v>8</v>
       </c>
       <c r="D5" s="7">
-        <v>37</v>
+        <v>7</v>
       </c>
       <c r="E5" s="4">
-        <v>10.42307692307692</v>
-      </c>
-      <c r="F5">
+        <v>10.423076923076923</v>
+      </c>
+      <c r="F5" s="7">
         <v>22.6</v>
       </c>
-      <c r="G5" s="9"/>
+      <c r="G5" s="11"/>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -1829,15 +3004,15 @@
         <v>8</v>
       </c>
       <c r="D6" s="7">
-        <v>51</v>
+        <v>6</v>
       </c>
       <c r="E6" s="4">
-        <v>10.42307692307692</v>
-      </c>
-      <c r="F6">
+        <v>10.423076923076923</v>
+      </c>
+      <c r="F6" s="7">
         <v>22.7</v>
       </c>
-      <c r="G6" s="9"/>
+      <c r="G6" s="11"/>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -1847,15 +3022,15 @@
         <v>8</v>
       </c>
       <c r="D7" s="7">
-        <v>65</v>
+        <v>5</v>
       </c>
       <c r="E7" s="4">
         <v>8.5192307692307701</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="7">
         <v>22.7</v>
       </c>
-      <c r="G7" s="9"/>
+      <c r="G7" s="11"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
@@ -1865,15 +3040,15 @@
         <v>8</v>
       </c>
       <c r="D8" s="7">
-        <v>79</v>
+        <v>4</v>
       </c>
       <c r="E8" s="4">
-        <v>10.21153846153846</v>
-      </c>
-      <c r="F8">
+        <v>10.211538461538462</v>
+      </c>
+      <c r="F8" s="7">
         <v>22.8</v>
       </c>
-      <c r="G8" s="9"/>
+      <c r="G8" s="11"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
@@ -1883,15 +3058,15 @@
         <v>8</v>
       </c>
       <c r="D9" s="7">
-        <v>96</v>
+        <v>3</v>
       </c>
       <c r="E9" s="4">
         <v>8.5192307692307701</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="7">
         <v>22.8</v>
       </c>
-      <c r="G9" s="9"/>
+      <c r="G9" s="11"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
@@ -1901,15 +3076,15 @@
         <v>8</v>
       </c>
       <c r="D10" s="7">
-        <v>111</v>
+        <v>2</v>
       </c>
       <c r="E10" s="4">
-        <v>10.63461538461539</v>
-      </c>
-      <c r="F10">
+        <v>10.634615384615385</v>
+      </c>
+      <c r="F10" s="7">
         <v>22.8</v>
       </c>
-      <c r="G10" s="9"/>
+      <c r="G10" s="11"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
@@ -1919,15 +3094,15 @@
         <v>8</v>
       </c>
       <c r="D11" s="7">
-        <v>129</v>
+        <v>11</v>
       </c>
       <c r="E11" s="4">
         <v>9.365384615384615</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="7">
         <v>23</v>
       </c>
-      <c r="G11" s="9"/>
+      <c r="G11" s="11"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1937,15 +3112,15 @@
         <v>8</v>
       </c>
       <c r="D12" s="7">
-        <v>148</v>
+        <v>11</v>
       </c>
       <c r="E12" s="4">
         <v>9.365384615384615</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="7">
         <v>23</v>
       </c>
-      <c r="G12" s="9"/>
+      <c r="G12" s="11"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
@@ -1955,17 +3130,15 @@
         <v>8</v>
       </c>
       <c r="D13" s="7">
-        <v>148</v>
+        <v>1</v>
       </c>
       <c r="E13" s="4">
-        <v>11.05769230769231</v>
-      </c>
-      <c r="F13">
+        <v>11.057692307692308</v>
+      </c>
+      <c r="F13" s="7">
         <v>23.4</v>
       </c>
-      <c r="G13" s="8">
-        <v>2</v>
-      </c>
+      <c r="G13" s="10"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
@@ -1975,15 +3148,15 @@
         <v>8</v>
       </c>
       <c r="D14" s="7">
-        <v>166</v>
+        <v>1</v>
       </c>
       <c r="E14" s="4">
-        <v>10.63461538461539</v>
-      </c>
-      <c r="F14">
+        <v>10.634615384615385</v>
+      </c>
+      <c r="F14" s="7">
         <v>23.4</v>
       </c>
-      <c r="G14" s="9"/>
+      <c r="G14" s="11"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
@@ -1993,15 +3166,15 @@
         <v>8</v>
       </c>
       <c r="D15" s="7">
-        <v>185</v>
+        <v>36</v>
       </c>
       <c r="E15" s="4">
-        <v>11.90384615384615</v>
-      </c>
-      <c r="F15">
+        <v>11.903846153846153</v>
+      </c>
+      <c r="F15" s="7">
         <v>23.7</v>
       </c>
-      <c r="G15" s="9"/>
+      <c r="G15" s="11"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
@@ -2011,15 +3184,15 @@
         <v>8</v>
       </c>
       <c r="D16" s="7">
-        <v>203</v>
+        <v>23</v>
       </c>
       <c r="E16" s="4">
         <v>11.26923076923077</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="7">
         <v>23.7</v>
       </c>
-      <c r="G16" s="9"/>
+      <c r="G16" s="11"/>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
@@ -2029,15 +3202,15 @@
         <v>8</v>
       </c>
       <c r="D17" s="7">
-        <v>218</v>
+        <v>12</v>
       </c>
       <c r="E17" s="4">
-        <v>12.32692307692308</v>
-      </c>
-      <c r="F17">
+        <v>12.326923076923077</v>
+      </c>
+      <c r="F17" s="7">
         <v>24.1</v>
       </c>
-      <c r="G17" s="9"/>
+      <c r="G17" s="11"/>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
@@ -2047,15 +3220,15 @@
         <v>8</v>
       </c>
       <c r="D18" s="7">
-        <v>235</v>
+        <v>24</v>
       </c>
       <c r="E18" s="4">
         <v>10</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="7">
         <v>24.5</v>
       </c>
-      <c r="G18" s="9"/>
+      <c r="G18" s="11"/>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
@@ -2065,15 +3238,15 @@
         <v>8</v>
       </c>
       <c r="D19" s="7">
-        <v>249</v>
+        <v>50</v>
       </c>
       <c r="E19" s="4">
-        <v>10.42307692307692</v>
-      </c>
-      <c r="F19">
+        <v>10.423076923076923</v>
+      </c>
+      <c r="F19" s="7">
         <v>24.6</v>
       </c>
-      <c r="G19" s="9"/>
+      <c r="G19" s="11"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
@@ -2083,15 +3256,15 @@
         <v>8</v>
       </c>
       <c r="D20" s="7">
-        <v>263</v>
+        <v>64</v>
       </c>
       <c r="E20" s="4">
         <v>11.48076923076923</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="7">
         <v>25.4</v>
       </c>
-      <c r="G20" s="9"/>
+      <c r="G20" s="11"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
@@ -2101,15 +3274,15 @@
         <v>8</v>
       </c>
       <c r="D21" s="7">
-        <v>277</v>
+        <v>37</v>
       </c>
       <c r="E21" s="4">
-        <v>12.11538461538462</v>
-      </c>
-      <c r="F21">
+        <v>12.115384615384617</v>
+      </c>
+      <c r="F21" s="7">
         <v>25.8</v>
       </c>
-      <c r="G21" s="9"/>
+      <c r="G21" s="11"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
@@ -2119,15 +3292,15 @@
         <v>8</v>
       </c>
       <c r="D22" s="7">
-        <v>290</v>
+        <v>78</v>
       </c>
       <c r="E22" s="4">
-        <v>11.05769230769231</v>
-      </c>
-      <c r="F22">
+        <v>11.057692307692308</v>
+      </c>
+      <c r="F22" s="7">
         <v>26</v>
       </c>
-      <c r="G22" s="9"/>
+      <c r="G22" s="11"/>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
@@ -2137,15 +3310,15 @@
         <v>8</v>
       </c>
       <c r="D23" s="7">
-        <v>302</v>
+        <v>51</v>
       </c>
       <c r="E23" s="4">
-        <v>12.32692307692308</v>
-      </c>
-      <c r="F23">
+        <v>12.326923076923077</v>
+      </c>
+      <c r="F23" s="7">
         <v>26.4</v>
       </c>
-      <c r="G23" s="9"/>
+      <c r="G23" s="11"/>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
@@ -2155,17 +3328,15 @@
         <v>8</v>
       </c>
       <c r="D24" s="7">
-        <v>302</v>
+        <v>65</v>
       </c>
       <c r="E24" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F24">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F24" s="7">
         <v>27</v>
       </c>
-      <c r="G24" s="8">
-        <v>3</v>
-      </c>
+      <c r="G24" s="10"/>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
@@ -2175,15 +3346,15 @@
         <v>8</v>
       </c>
       <c r="D25" s="7">
-        <v>303</v>
+        <v>95</v>
       </c>
       <c r="E25" s="4">
-        <v>12.32692307692308</v>
-      </c>
-      <c r="F25">
+        <v>12.326923076923077</v>
+      </c>
+      <c r="F25" s="7">
         <v>27.1</v>
       </c>
-      <c r="G25" s="9"/>
+      <c r="G25" s="11"/>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
@@ -2193,15 +3364,15 @@
         <v>8</v>
       </c>
       <c r="D26" s="7">
-        <v>304</v>
+        <v>79</v>
       </c>
       <c r="E26" s="4">
         <v>12.75</v>
       </c>
-      <c r="F26">
+      <c r="F26" s="7">
         <v>27.4</v>
       </c>
-      <c r="G26" s="9"/>
+      <c r="G26" s="11"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
@@ -2211,15 +3382,15 @@
         <v>8</v>
       </c>
       <c r="D27" s="7">
-        <v>305</v>
+        <v>110</v>
       </c>
       <c r="E27" s="4">
-        <v>11.69230769230769</v>
-      </c>
-      <c r="F27">
+        <v>11.692307692307693</v>
+      </c>
+      <c r="F27" s="7">
         <v>27.5</v>
       </c>
-      <c r="G27" s="9"/>
+      <c r="G27" s="11"/>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
@@ -2229,15 +3400,15 @@
         <v>8</v>
       </c>
       <c r="D28" s="7">
-        <v>306</v>
+        <v>96</v>
       </c>
       <c r="E28" s="4">
-        <v>12.11538461538462</v>
-      </c>
-      <c r="F28">
+        <v>12.115384615384617</v>
+      </c>
+      <c r="F28" s="7">
         <v>27.8</v>
       </c>
-      <c r="G28" s="9"/>
+      <c r="G28" s="11"/>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
@@ -2247,15 +3418,15 @@
         <v>8</v>
       </c>
       <c r="D29" s="7">
-        <v>307</v>
+        <v>128</v>
       </c>
       <c r="E29" s="4">
-        <v>13.17307692307692</v>
-      </c>
-      <c r="F29">
+        <v>13.173076923076923</v>
+      </c>
+      <c r="F29" s="7">
         <v>27.9</v>
       </c>
-      <c r="G29" s="9"/>
+      <c r="G29" s="11"/>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
@@ -2265,15 +3436,15 @@
         <v>8</v>
       </c>
       <c r="D30" s="7">
-        <v>308</v>
+        <v>111</v>
       </c>
       <c r="E30" s="4">
-        <v>12.96153846153846</v>
-      </c>
-      <c r="F30">
+        <v>12.961538461538462</v>
+      </c>
+      <c r="F30" s="7">
         <v>28.1</v>
       </c>
-      <c r="G30" s="9"/>
+      <c r="G30" s="11"/>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
@@ -2283,15 +3454,15 @@
         <v>8</v>
       </c>
       <c r="D31" s="7">
-        <v>309</v>
+        <v>147</v>
       </c>
       <c r="E31" s="4">
-        <v>13.38461538461539</v>
-      </c>
-      <c r="F31">
+        <v>13.384615384615385</v>
+      </c>
+      <c r="F31" s="7">
         <v>28.2</v>
       </c>
-      <c r="G31" s="9"/>
+      <c r="G31" s="11"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
@@ -2301,15 +3472,15 @@
         <v>8</v>
       </c>
       <c r="D32" s="7">
-        <v>310</v>
+        <v>129</v>
       </c>
       <c r="E32" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F32">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F32" s="7">
         <v>28.5</v>
       </c>
-      <c r="G32" s="9"/>
+      <c r="G32" s="11"/>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -2319,15 +3490,15 @@
         <v>8</v>
       </c>
       <c r="D33" s="7">
-        <v>311</v>
+        <v>184</v>
       </c>
       <c r="E33" s="4">
-        <v>13.976923076923081</v>
-      </c>
-      <c r="F33">
+        <v>13.976923076923077</v>
+      </c>
+      <c r="F33" s="7">
         <v>28.8</v>
       </c>
-      <c r="G33" s="9"/>
+      <c r="G33" s="11"/>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
@@ -2337,15 +3508,15 @@
         <v>8</v>
       </c>
       <c r="D34" s="7">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="E34" s="4">
-        <v>13.59615384615385</v>
-      </c>
-      <c r="F34">
+        <v>13.596153846153847</v>
+      </c>
+      <c r="F34" s="7">
         <v>29</v>
       </c>
-      <c r="G34" s="9"/>
+      <c r="G34" s="11"/>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
@@ -2355,17 +3526,15 @@
         <v>8</v>
       </c>
       <c r="D35" s="7">
-        <v>312</v>
+        <v>165</v>
       </c>
       <c r="E35" s="4">
-        <v>13.59615384615385</v>
-      </c>
-      <c r="F35">
+        <v>13.596153846153847</v>
+      </c>
+      <c r="F35" s="7">
         <v>29</v>
       </c>
-      <c r="G35" s="8">
-        <v>4</v>
-      </c>
+      <c r="G35" s="10"/>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
@@ -2375,15 +3544,15 @@
         <v>8</v>
       </c>
       <c r="D36" s="7">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="E36" s="4">
-        <v>12.45384615384615</v>
-      </c>
-      <c r="F36">
+        <v>12.453846153846154</v>
+      </c>
+      <c r="F36" s="7">
         <v>29.4</v>
       </c>
-      <c r="G36" s="9"/>
+      <c r="G36" s="11"/>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
@@ -2393,15 +3562,15 @@
         <v>8</v>
       </c>
       <c r="D37" s="7">
-        <v>289</v>
+        <v>148</v>
       </c>
       <c r="E37" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F37">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F37" s="7">
         <v>29.7</v>
       </c>
-      <c r="G37" s="9"/>
+      <c r="G37" s="11"/>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
@@ -2411,15 +3580,15 @@
         <v>8</v>
       </c>
       <c r="D38" s="7">
-        <v>276</v>
+        <v>148</v>
       </c>
       <c r="E38" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F38">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F38" s="7">
         <v>29.7</v>
       </c>
-      <c r="G38" s="9"/>
+      <c r="G38" s="11"/>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
@@ -2429,15 +3598,15 @@
         <v>8</v>
       </c>
       <c r="D39" s="7">
-        <v>262</v>
+        <v>166</v>
       </c>
       <c r="E39" s="4">
         <v>12.75</v>
       </c>
-      <c r="F39">
+      <c r="F39" s="7">
         <v>29.7</v>
       </c>
-      <c r="G39" s="9"/>
+      <c r="G39" s="11"/>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
@@ -2447,15 +3616,15 @@
         <v>8</v>
       </c>
       <c r="D40" s="7">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="E40" s="4">
-        <v>13.04615384615385</v>
-      </c>
-      <c r="F40">
+        <v>13.046153846153846</v>
+      </c>
+      <c r="F40" s="7">
         <v>30</v>
       </c>
-      <c r="G40" s="9"/>
+      <c r="G40" s="11"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
@@ -2465,15 +3634,15 @@
         <v>8</v>
       </c>
       <c r="D41" s="7">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="E41" s="4">
-        <v>13.17307692307692</v>
-      </c>
-      <c r="F41">
+        <v>13.173076923076923</v>
+      </c>
+      <c r="F41" s="7">
         <v>30.2</v>
       </c>
-      <c r="G41" s="9"/>
+      <c r="G41" s="11"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
@@ -2483,15 +3652,15 @@
         <v>8</v>
       </c>
       <c r="D42" s="7">
-        <v>217</v>
+        <v>234</v>
       </c>
       <c r="E42" s="4">
         <v>13.63846153846154</v>
       </c>
-      <c r="F42">
+      <c r="F42" s="7">
         <v>30.5</v>
       </c>
-      <c r="G42" s="9"/>
+      <c r="G42" s="11"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
@@ -2501,15 +3670,15 @@
         <v>8</v>
       </c>
       <c r="D43" s="7">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="E43" s="4">
-        <v>12.96153846153846</v>
-      </c>
-      <c r="F43">
+        <v>12.961538461538462</v>
+      </c>
+      <c r="F43" s="7">
         <v>30.8</v>
       </c>
-      <c r="G43" s="9"/>
+      <c r="G43" s="11"/>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
@@ -2519,15 +3688,15 @@
         <v>8</v>
       </c>
       <c r="D44" s="7">
-        <v>184</v>
+        <v>248</v>
       </c>
       <c r="E44" s="4">
-        <v>13.80769230769231</v>
-      </c>
-      <c r="F44">
+        <v>13.807692307692308</v>
+      </c>
+      <c r="F44" s="7">
         <v>30.9</v>
       </c>
-      <c r="G44" s="9"/>
+      <c r="G44" s="11"/>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
@@ -2537,15 +3706,15 @@
         <v>8</v>
       </c>
       <c r="D45" s="7">
-        <v>165</v>
+        <v>262</v>
       </c>
       <c r="E45" s="4">
-        <v>14.61153846153846</v>
-      </c>
-      <c r="F45">
+        <v>14.611538461538462</v>
+      </c>
+      <c r="F45" s="7">
         <v>31.2</v>
       </c>
-      <c r="G45" s="9"/>
+      <c r="G45" s="11"/>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
@@ -2555,17 +3724,15 @@
         <v>8</v>
       </c>
       <c r="D46" s="7">
-        <v>165</v>
+        <v>218</v>
       </c>
       <c r="E46" s="4">
         <v>12.75</v>
       </c>
-      <c r="F46">
+      <c r="F46" s="7">
         <v>31.3</v>
       </c>
-      <c r="G46" s="8">
-        <v>5</v>
-      </c>
+      <c r="G46" s="10"/>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
@@ -2575,15 +3742,15 @@
         <v>8</v>
       </c>
       <c r="D47" s="7">
-        <v>147</v>
+        <v>276</v>
       </c>
       <c r="E47" s="4">
-        <v>13.723076923076921</v>
-      </c>
-      <c r="F47">
+        <v>13.723076923076924</v>
+      </c>
+      <c r="F47" s="7">
         <v>31.3</v>
       </c>
-      <c r="G47" s="9"/>
+      <c r="G47" s="11"/>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
@@ -2593,15 +3760,15 @@
         <v>8</v>
       </c>
       <c r="D48" s="7">
-        <v>128</v>
+        <v>301</v>
       </c>
       <c r="E48" s="4">
-        <v>15.542307692307689</v>
-      </c>
-      <c r="F48">
+        <v>15.542307692307693</v>
+      </c>
+      <c r="F48" s="7">
         <v>31.4</v>
       </c>
-      <c r="G48" s="9"/>
+      <c r="G48" s="11"/>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
@@ -2611,15 +3778,15 @@
         <v>8</v>
       </c>
       <c r="D49" s="7">
-        <v>110</v>
+        <v>289</v>
       </c>
       <c r="E49" s="4">
-        <v>13.892307692307689</v>
-      </c>
-      <c r="F49">
+        <v>13.892307692307693</v>
+      </c>
+      <c r="F49" s="7">
         <v>31.4</v>
       </c>
-      <c r="G49" s="9"/>
+      <c r="G49" s="11"/>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
@@ -2629,15 +3796,15 @@
         <v>8</v>
       </c>
       <c r="D50" s="7">
-        <v>95</v>
+        <v>304</v>
       </c>
       <c r="E50" s="4">
-        <v>12.32692307692308</v>
-      </c>
-      <c r="F50">
+        <v>12.326923076923077</v>
+      </c>
+      <c r="F50" s="7">
         <v>31.5</v>
       </c>
-      <c r="G50" s="9"/>
+      <c r="G50" s="11"/>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
@@ -2647,15 +3814,15 @@
         <v>8</v>
       </c>
       <c r="D51" s="7">
-        <v>78</v>
+        <v>303</v>
       </c>
       <c r="E51" s="4">
-        <v>13.06730769230769</v>
-      </c>
-      <c r="F51">
+        <v>13.067307692307693</v>
+      </c>
+      <c r="F51" s="7">
         <v>31.6</v>
       </c>
-      <c r="G51" s="9"/>
+      <c r="G51" s="11"/>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
@@ -2665,15 +3832,15 @@
         <v>8</v>
       </c>
       <c r="D52" s="7">
-        <v>64</v>
+        <v>305</v>
       </c>
       <c r="E52" s="4">
         <v>12.64423076923077</v>
       </c>
-      <c r="F52">
+      <c r="F52" s="7">
         <v>31.6</v>
       </c>
-      <c r="G52" s="9"/>
+      <c r="G52" s="11"/>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
@@ -2683,15 +3850,15 @@
         <v>8</v>
       </c>
       <c r="D53" s="7">
-        <v>50</v>
+        <v>311</v>
       </c>
       <c r="E53" s="4">
         <v>14.125</v>
       </c>
-      <c r="F53">
+      <c r="F53" s="7">
         <v>31.6</v>
       </c>
-      <c r="G53" s="9"/>
+      <c r="G53" s="11"/>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
@@ -2701,15 +3868,15 @@
         <v>8</v>
       </c>
       <c r="D54" s="7">
-        <v>36</v>
+        <v>235</v>
       </c>
       <c r="E54" s="4">
-        <v>12.96153846153846</v>
-      </c>
-      <c r="F54">
+        <v>12.961538461538462</v>
+      </c>
+      <c r="F54" s="7">
         <v>31.7</v>
       </c>
-      <c r="G54" s="9"/>
+      <c r="G54" s="11"/>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
@@ -2719,15 +3886,15 @@
         <v>8</v>
       </c>
       <c r="D55" s="7">
-        <v>23</v>
+        <v>306</v>
       </c>
       <c r="E55" s="4">
-        <v>13.17307692307692</v>
-      </c>
-      <c r="F55">
+        <v>13.173076923076923</v>
+      </c>
+      <c r="F55" s="7">
         <v>31.7</v>
       </c>
-      <c r="G55" s="9"/>
+      <c r="G55" s="11"/>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
@@ -2737,15 +3904,15 @@
         <v>8</v>
       </c>
       <c r="D56" s="7">
-        <v>11</v>
+        <v>310</v>
       </c>
       <c r="E56" s="4">
         <v>15.28846153846154</v>
       </c>
-      <c r="F56">
+      <c r="F56" s="7">
         <v>31.7</v>
       </c>
-      <c r="G56" s="9"/>
+      <c r="G56" s="11"/>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
@@ -2755,17 +3922,15 @@
         <v>8</v>
       </c>
       <c r="D57" s="7">
-        <v>11</v>
+        <v>307</v>
       </c>
       <c r="E57" s="4">
-        <v>13.06730769230769</v>
-      </c>
-      <c r="F57">
+        <v>13.067307692307693</v>
+      </c>
+      <c r="F57" s="7">
         <v>31.8</v>
       </c>
-      <c r="G57" s="8">
-        <v>6</v>
-      </c>
+      <c r="G57" s="10"/>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
@@ -2775,15 +3940,15 @@
         <v>8</v>
       </c>
       <c r="D58" s="7">
-        <v>10</v>
+        <v>308</v>
       </c>
       <c r="E58" s="4">
-        <v>12.96153846153846</v>
-      </c>
-      <c r="F58">
+        <v>12.961538461538462</v>
+      </c>
+      <c r="F58" s="7">
         <v>31.8</v>
       </c>
-      <c r="G58" s="9"/>
+      <c r="G58" s="11"/>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
@@ -2793,15 +3958,15 @@
         <v>8</v>
       </c>
       <c r="D59" s="7">
-        <v>9</v>
+        <v>309</v>
       </c>
       <c r="E59" s="4">
-        <v>13.27884615384615</v>
-      </c>
-      <c r="F59">
+        <v>13.278846153846153</v>
+      </c>
+      <c r="F59" s="7">
         <v>31.8</v>
       </c>
-      <c r="G59" s="9"/>
+      <c r="G59" s="11"/>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
@@ -2811,15 +3976,15 @@
         <v>8</v>
       </c>
       <c r="D60" s="7">
-        <v>8</v>
+        <v>249</v>
       </c>
       <c r="E60" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F60">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F60" s="7">
         <v>31.9</v>
       </c>
-      <c r="G60" s="9"/>
+      <c r="G60" s="11"/>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
@@ -2829,15 +3994,15 @@
         <v>8</v>
       </c>
       <c r="D61" s="7">
-        <v>7</v>
+        <v>290</v>
       </c>
       <c r="E61" s="4">
-        <v>12.32692307692308</v>
-      </c>
-      <c r="F61">
+        <v>12.326923076923077</v>
+      </c>
+      <c r="F61" s="7">
         <v>31.9</v>
       </c>
-      <c r="G61" s="9"/>
+      <c r="G61" s="11"/>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
@@ -2847,15 +4012,15 @@
         <v>8</v>
       </c>
       <c r="D62" s="7">
-        <v>6</v>
+        <v>263</v>
       </c>
       <c r="E62" s="4">
-        <v>12.53846153846154</v>
-      </c>
-      <c r="F62">
+        <v>12.538461538461538</v>
+      </c>
+      <c r="F62" s="7">
         <v>32</v>
       </c>
-      <c r="G62" s="9"/>
+      <c r="G62" s="11"/>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
@@ -2865,15 +4030,15 @@
         <v>8</v>
       </c>
       <c r="D63" s="7">
-        <v>5</v>
+        <v>277</v>
       </c>
       <c r="E63" s="4">
-        <v>13.80769230769231</v>
-      </c>
-      <c r="F63">
+        <v>13.807692307692308</v>
+      </c>
+      <c r="F63" s="7">
         <v>32</v>
       </c>
-      <c r="G63" s="9"/>
+      <c r="G63" s="11"/>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
@@ -2883,15 +4048,15 @@
         <v>8</v>
       </c>
       <c r="D64" s="7">
-        <v>4</v>
+        <v>312</v>
       </c>
       <c r="E64" s="4">
-        <v>13.59615384615385</v>
-      </c>
-      <c r="F64">
+        <v>13.596153846153847</v>
+      </c>
+      <c r="F64" s="7">
         <v>32.1</v>
       </c>
-      <c r="G64" s="9"/>
+      <c r="G64" s="11"/>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
@@ -2901,15 +4066,15 @@
         <v>8</v>
       </c>
       <c r="D65" s="7">
-        <v>3</v>
+        <v>312</v>
       </c>
       <c r="E65" s="4">
-        <v>13.59615384615385</v>
-      </c>
-      <c r="F65">
+        <v>13.596153846153847</v>
+      </c>
+      <c r="F65" s="7">
         <v>32.1</v>
       </c>
-      <c r="G65" s="9"/>
+      <c r="G65" s="11"/>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
@@ -2919,15 +4084,15 @@
         <v>8</v>
       </c>
       <c r="D66" s="7">
-        <v>2</v>
+        <v>302</v>
       </c>
       <c r="E66" s="4">
-        <v>14.23076923076923</v>
-      </c>
-      <c r="F66">
+        <v>14.230769230769232</v>
+      </c>
+      <c r="F66" s="7">
         <v>32.5</v>
       </c>
-      <c r="G66" s="9"/>
+      <c r="G66" s="11"/>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
@@ -2937,15 +4102,15 @@
         <v>8</v>
       </c>
       <c r="D67" s="7">
-        <v>1</v>
+        <v>302</v>
       </c>
       <c r="E67" s="4">
-        <v>14.23076923076923</v>
-      </c>
-      <c r="F67">
+        <v>14.230769230769232</v>
+      </c>
+      <c r="F67" s="7">
         <v>32.5</v>
       </c>
-      <c r="G67" s="9"/>
+      <c r="G67" s="11"/>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
@@ -2955,17 +4120,15 @@
         <v>15</v>
       </c>
       <c r="D68" s="7">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="E68" s="4">
-        <v>11.265384615384621</v>
-      </c>
-      <c r="F68">
+        <v>11.265384615384615</v>
+      </c>
+      <c r="F68" s="7">
         <v>28.5</v>
       </c>
-      <c r="G68" s="8">
-        <v>1</v>
-      </c>
+      <c r="G68" s="10"/>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
@@ -2975,15 +4138,15 @@
         <v>15</v>
       </c>
       <c r="D69" s="7">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="E69" s="4">
-        <v>14.015384615384621</v>
-      </c>
-      <c r="F69">
+        <v>14.015384615384615</v>
+      </c>
+      <c r="F69" s="7">
         <v>28.7</v>
       </c>
-      <c r="G69" s="9"/>
+      <c r="G69" s="11"/>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
@@ -2993,15 +4156,15 @@
         <v>15</v>
       </c>
       <c r="D70" s="7">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E70" s="4">
-        <v>12.32307692307692</v>
-      </c>
-      <c r="F70">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F70" s="7">
         <v>28.8</v>
       </c>
-      <c r="G70" s="9"/>
+      <c r="G70" s="11"/>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
@@ -3011,15 +4174,15 @@
         <v>15</v>
       </c>
       <c r="D71" s="7">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="E71" s="4">
-        <v>13.38076923076923</v>
-      </c>
-      <c r="F71">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F71" s="7">
         <v>29</v>
       </c>
-      <c r="G71" s="9"/>
+      <c r="G71" s="11"/>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
@@ -3029,15 +4192,15 @@
         <v>15</v>
       </c>
       <c r="D72" s="7">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="E72" s="4">
-        <v>13.38076923076923</v>
-      </c>
-      <c r="F72">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F72" s="7">
         <v>29</v>
       </c>
-      <c r="G72" s="9"/>
+      <c r="G72" s="11"/>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
@@ -3047,15 +4210,15 @@
         <v>15</v>
       </c>
       <c r="D73" s="7">
-        <v>65</v>
+        <v>9</v>
       </c>
       <c r="E73" s="4">
-        <v>12.746153846153851</v>
-      </c>
-      <c r="F73">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F73" s="7">
         <v>29</v>
       </c>
-      <c r="G73" s="9"/>
+      <c r="G73" s="11"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
@@ -3065,15 +4228,15 @@
         <v>15</v>
       </c>
       <c r="D74" s="7">
-        <v>79</v>
+        <v>50</v>
       </c>
       <c r="E74" s="4">
-        <v>13.38076923076923</v>
-      </c>
-      <c r="F74">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F74" s="7">
         <v>29.2</v>
       </c>
-      <c r="G74" s="9"/>
+      <c r="G74" s="11"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
@@ -3083,15 +4246,15 @@
         <v>15</v>
       </c>
       <c r="D75" s="7">
-        <v>96</v>
+        <v>8</v>
       </c>
       <c r="E75" s="4">
         <v>11.9</v>
       </c>
-      <c r="F75">
+      <c r="F75" s="7">
         <v>29.4</v>
       </c>
-      <c r="G75" s="9"/>
+      <c r="G75" s="11"/>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
@@ -3101,15 +4264,15 @@
         <v>15</v>
       </c>
       <c r="D76" s="7">
-        <v>111</v>
+        <v>64</v>
       </c>
       <c r="E76" s="4">
         <v>13.16923076923077</v>
       </c>
-      <c r="F76">
+      <c r="F76" s="7">
         <v>29.5</v>
       </c>
-      <c r="G76" s="9"/>
+      <c r="G76" s="11"/>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
@@ -3119,15 +4282,15 @@
         <v>15</v>
       </c>
       <c r="D77" s="7">
-        <v>129</v>
+        <v>78</v>
       </c>
       <c r="E77" s="4">
-        <v>13.38076923076923</v>
-      </c>
-      <c r="F77">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F77" s="7">
         <v>29.7</v>
       </c>
-      <c r="G77" s="9"/>
+      <c r="G77" s="11"/>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
@@ -3137,1026 +4300,4462 @@
         <v>15</v>
       </c>
       <c r="D78" s="7">
-        <v>148</v>
+        <v>7</v>
       </c>
       <c r="E78" s="4">
-        <v>12.957692307692311</v>
-      </c>
-      <c r="F78">
+        <v>12.957692307692309</v>
+      </c>
+      <c r="F78" s="7">
         <v>29.7</v>
       </c>
-      <c r="G78" s="9"/>
+      <c r="G78" s="11"/>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>7</v>
       </c>
-      <c r="B79" t="s">
-        <v>16</v>
+      <c r="B79" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D79" s="7">
-        <v>11</v>
+        <v>165</v>
       </c>
       <c r="E79" s="4">
-        <v>13.0634615384615</v>
-      </c>
-      <c r="F79">
-        <v>29.85</v>
-      </c>
-      <c r="G79" s="8">
-        <v>6</v>
-      </c>
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F79" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G79" s="10"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>7</v>
       </c>
-      <c r="B80" t="s">
-        <v>16</v>
+      <c r="B80" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D80" s="7">
-        <v>10</v>
+        <v>147</v>
       </c>
       <c r="E80" s="4">
-        <v>13.0846153846154</v>
-      </c>
-      <c r="F80">
-        <v>29.96</v>
-      </c>
-      <c r="G80" s="9"/>
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F80" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G80" s="11"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>7</v>
       </c>
-      <c r="B81" t="s">
-        <v>16</v>
+      <c r="B81" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D81" s="7">
-        <v>9</v>
+        <v>128</v>
       </c>
       <c r="E81" s="4">
-        <v>13.1057692307692</v>
-      </c>
-      <c r="F81">
-        <v>30.07</v>
-      </c>
-      <c r="G81" s="9"/>
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F81" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G81" s="11"/>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>7</v>
       </c>
-      <c r="B82" t="s">
-        <v>16</v>
+      <c r="B82" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D82" s="7">
-        <v>8</v>
+        <v>95</v>
       </c>
       <c r="E82" s="4">
-        <v>13.1269230769231</v>
-      </c>
-      <c r="F82">
-        <v>30.18</v>
-      </c>
-      <c r="G82" s="9"/>
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F82" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G82" s="11"/>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>7</v>
       </c>
-      <c r="B83" t="s">
-        <v>16</v>
+      <c r="B83" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D83" s="7">
-        <v>7</v>
+        <v>110</v>
       </c>
       <c r="E83" s="4">
-        <v>13.1480769230769</v>
-      </c>
-      <c r="F83">
-        <v>30.29</v>
-      </c>
-      <c r="G83" s="9"/>
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F83" s="7">
+        <v>30</v>
+      </c>
+      <c r="G83" s="11"/>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>7</v>
       </c>
-      <c r="B84" t="s">
-        <v>16</v>
+      <c r="B84" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D84" s="7">
         <v>6</v>
       </c>
       <c r="E84" s="4">
-        <v>13.169230769230801</v>
-      </c>
-      <c r="F84">
-        <v>30.4</v>
-      </c>
-      <c r="G84" s="9"/>
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F84" s="7">
+        <v>30</v>
+      </c>
+      <c r="G84" s="11"/>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>7</v>
       </c>
-      <c r="B85" t="s">
-        <v>16</v>
+      <c r="B85" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D85" s="7">
         <v>5</v>
       </c>
       <c r="E85" s="4">
-        <v>13.1903846153846</v>
-      </c>
-      <c r="F85">
-        <v>30.51</v>
-      </c>
-      <c r="G85" s="9"/>
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F85" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G85" s="11"/>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>7</v>
       </c>
-      <c r="B86" t="s">
-        <v>16</v>
+      <c r="B86" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D86" s="7">
         <v>4</v>
       </c>
       <c r="E86" s="4">
-        <v>13.211538461538501</v>
-      </c>
-      <c r="F86">
-        <v>30.62</v>
-      </c>
-      <c r="G86" s="9"/>
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F86" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G86" s="11"/>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>7</v>
       </c>
-      <c r="B87" t="s">
-        <v>16</v>
+      <c r="B87" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D87" s="7">
         <v>3</v>
       </c>
       <c r="E87" s="4">
-        <v>13.2326923076923</v>
-      </c>
-      <c r="F87">
-        <v>30.73</v>
-      </c>
-      <c r="G87" s="9"/>
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F87" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G87" s="11"/>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>7</v>
       </c>
-      <c r="B88" t="s">
-        <v>16</v>
+      <c r="B88" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D88" s="7">
         <v>2</v>
       </c>
       <c r="E88" s="4">
-        <v>13.253846153846199</v>
-      </c>
-      <c r="F88">
-        <v>30.84</v>
-      </c>
-      <c r="G88" s="9"/>
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F88" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G88" s="11"/>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>7</v>
       </c>
-      <c r="B89" t="s">
-        <v>16</v>
+      <c r="B89" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D89" s="7">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="E89" s="4">
-        <v>13.275</v>
-      </c>
-      <c r="F89">
-        <v>30.95</v>
-      </c>
-      <c r="G89" s="9"/>
+        <v>11.9</v>
+      </c>
+      <c r="F89" s="7">
+        <v>30.2</v>
+      </c>
+      <c r="G89" s="11"/>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>7</v>
       </c>
-      <c r="B90" t="s">
-        <v>16</v>
+      <c r="B90" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D90" s="7">
-        <v>165</v>
+        <v>184</v>
       </c>
       <c r="E90" s="4">
-        <v>13.296153846154001</v>
-      </c>
-      <c r="F90">
-        <v>31.06</v>
-      </c>
-      <c r="G90" s="8">
-        <v>5</v>
-      </c>
+        <v>13.126923076923077</v>
+      </c>
+      <c r="F90" s="7">
+        <v>30.2</v>
+      </c>
+      <c r="G90" s="10"/>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>7</v>
       </c>
-      <c r="B91" t="s">
-        <v>16</v>
+      <c r="B91" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D91" s="7">
-        <v>147</v>
+        <v>24</v>
       </c>
       <c r="E91" s="4">
-        <v>13.317307692307899</v>
-      </c>
-      <c r="F91">
-        <v>31.17</v>
-      </c>
-      <c r="G91" s="9"/>
+        <v>11.9</v>
+      </c>
+      <c r="F91" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="G91" s="11"/>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>7</v>
       </c>
-      <c r="B92" t="s">
-        <v>16</v>
+      <c r="B92" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D92" s="7">
-        <v>128</v>
+        <v>165</v>
       </c>
       <c r="E92" s="4">
-        <v>13.3384615384618</v>
-      </c>
-      <c r="F92">
-        <v>31.28</v>
-      </c>
-      <c r="G92" s="9"/>
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F92" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="G92" s="11"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>7</v>
       </c>
-      <c r="B93" t="s">
-        <v>16</v>
+      <c r="B93" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D93" s="7">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="E93" s="4">
-        <v>13.359615384615701</v>
-      </c>
-      <c r="F93">
-        <v>31.39</v>
-      </c>
-      <c r="G93" s="9"/>
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F93" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G93" s="11"/>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>7</v>
       </c>
-      <c r="B94" t="s">
-        <v>16</v>
+      <c r="B94" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D94" s="7">
-        <v>95</v>
+        <v>202</v>
       </c>
       <c r="E94" s="4">
-        <v>13.3807692307696</v>
-      </c>
-      <c r="F94">
-        <v>31.5</v>
-      </c>
-      <c r="G94" s="9"/>
+        <v>13.507692307692309</v>
+      </c>
+      <c r="F94" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G94" s="11"/>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>7</v>
       </c>
-      <c r="B95" t="s">
-        <v>16</v>
+      <c r="B95" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D95" s="7">
-        <v>78</v>
+        <v>1</v>
       </c>
       <c r="E95" s="4">
-        <v>13.4019230769235</v>
-      </c>
-      <c r="F95">
-        <v>31.61</v>
-      </c>
-      <c r="G95" s="9"/>
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F95" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G95" s="11"/>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>7</v>
       </c>
-      <c r="B96" t="s">
-        <v>16</v>
+      <c r="B96" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D96" s="7">
-        <v>64</v>
+        <v>37</v>
       </c>
       <c r="E96" s="4">
-        <v>13.423076923077399</v>
-      </c>
-      <c r="F96">
-        <v>31.72</v>
-      </c>
-      <c r="G96" s="9"/>
+        <v>12.111538461538462</v>
+      </c>
+      <c r="F96" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="G96" s="11"/>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>7</v>
       </c>
-      <c r="B97" t="s">
-        <v>16</v>
+      <c r="B97" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D97" s="7">
-        <v>50</v>
+        <v>217</v>
       </c>
       <c r="E97" s="4">
-        <v>13.4442307692313</v>
-      </c>
-      <c r="F97">
-        <v>31.83</v>
-      </c>
-      <c r="G97" s="9"/>
+        <v>13.042307692307693</v>
+      </c>
+      <c r="F97" s="7">
+        <v>31.2</v>
+      </c>
+      <c r="G97" s="11"/>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>7</v>
       </c>
-      <c r="B98" t="s">
-        <v>16</v>
+      <c r="B98" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D98" s="7">
-        <v>36</v>
+        <v>51</v>
       </c>
       <c r="E98" s="4">
-        <v>13.465384615385201</v>
-      </c>
-      <c r="F98">
-        <v>31.94</v>
-      </c>
-      <c r="G98" s="9"/>
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F98" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G98" s="11"/>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>7</v>
       </c>
-      <c r="B99" t="s">
-        <v>16</v>
+      <c r="B99" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D99" s="7">
-        <v>23</v>
+        <v>111</v>
       </c>
       <c r="E99" s="4">
-        <v>13.4865384615391</v>
-      </c>
-      <c r="F99">
-        <v>32.049999999999997</v>
-      </c>
-      <c r="G99" s="9"/>
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F99" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G99" s="11"/>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>7</v>
       </c>
-      <c r="B100" t="s">
-        <v>16</v>
+      <c r="B100" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D100" s="7">
-        <v>11</v>
+        <v>129</v>
       </c>
       <c r="E100" s="4">
-        <v>13.507692307693</v>
-      </c>
-      <c r="F100">
-        <v>32.159999999999997</v>
-      </c>
-      <c r="G100" s="9"/>
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F100" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G100" s="11"/>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>7</v>
       </c>
-      <c r="B101" t="s">
-        <v>16</v>
+      <c r="B101" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D101" s="7">
-        <v>302</v>
+        <v>166</v>
       </c>
       <c r="E101" s="4">
-        <v>13.528846153846899</v>
-      </c>
-      <c r="F101">
-        <v>32.270000000000003</v>
-      </c>
-      <c r="G101" s="8">
-        <v>3</v>
-      </c>
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F101" s="7">
+        <v>31.4</v>
+      </c>
+      <c r="G101" s="10"/>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>7</v>
       </c>
-      <c r="B102" t="s">
-        <v>16</v>
+      <c r="B102" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D102" s="7">
-        <v>303</v>
+        <v>65</v>
       </c>
       <c r="E102" s="4">
-        <v>13.5500000000008</v>
-      </c>
-      <c r="F102">
-        <v>32.380000000000003</v>
-      </c>
-      <c r="G102" s="9"/>
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F102" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G102" s="11"/>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>7</v>
       </c>
-      <c r="B103" t="s">
-        <v>16</v>
+      <c r="B103" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D103" s="7">
-        <v>304</v>
+        <v>96</v>
       </c>
       <c r="E103" s="4">
-        <v>13.571153846154701</v>
-      </c>
-      <c r="F103">
-        <v>32.49</v>
-      </c>
-      <c r="G103" s="9"/>
+        <v>11.9</v>
+      </c>
+      <c r="F103" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G103" s="11"/>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>7</v>
       </c>
-      <c r="B104" t="s">
-        <v>16</v>
+      <c r="B104" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D104" s="7">
-        <v>305</v>
+        <v>185</v>
       </c>
       <c r="E104" s="4">
-        <v>13.5923076923086</v>
-      </c>
-      <c r="F104">
-        <v>32.6</v>
-      </c>
-      <c r="G104" s="9"/>
+        <v>11.9</v>
+      </c>
+      <c r="F104" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G104" s="11"/>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>7</v>
       </c>
-      <c r="B105" t="s">
-        <v>16</v>
+      <c r="B105" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D105" s="7">
-        <v>306</v>
+        <v>79</v>
       </c>
       <c r="E105" s="4">
-        <v>13.6134615384625</v>
-      </c>
-      <c r="F105">
-        <v>32.71</v>
-      </c>
-      <c r="G105" s="9"/>
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F105" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G105" s="11"/>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>7</v>
       </c>
-      <c r="B106" t="s">
-        <v>16</v>
+      <c r="B106" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D106" s="7">
-        <v>307</v>
+        <v>263</v>
       </c>
       <c r="E106" s="4">
-        <v>13.634615384616399</v>
-      </c>
-      <c r="F106">
-        <v>32.82</v>
-      </c>
-      <c r="G106" s="9"/>
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F106" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G106" s="11"/>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>7</v>
       </c>
-      <c r="B107" t="s">
-        <v>16</v>
+      <c r="B107" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D107" s="7">
-        <v>308</v>
+        <v>277</v>
       </c>
       <c r="E107" s="4">
-        <v>13.6557692307703</v>
-      </c>
-      <c r="F107">
-        <v>32.93</v>
-      </c>
-      <c r="G107" s="9"/>
+        <v>11.9</v>
+      </c>
+      <c r="F107" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G107" s="11"/>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>7</v>
       </c>
-      <c r="B108" t="s">
-        <v>16</v>
+      <c r="B108" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D108" s="7">
-        <v>309</v>
+        <v>290</v>
       </c>
       <c r="E108" s="4">
-        <v>13.676923076924201</v>
-      </c>
-      <c r="F108">
-        <v>33.04</v>
-      </c>
-      <c r="G108" s="9"/>
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F108" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G108" s="11"/>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>7</v>
       </c>
-      <c r="B109" t="s">
-        <v>16</v>
+      <c r="B109" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D109" s="7">
-        <v>310</v>
+        <v>234</v>
       </c>
       <c r="E109" s="4">
-        <v>13.6980769230781</v>
-      </c>
-      <c r="F109">
-        <v>33.15</v>
-      </c>
-      <c r="G109" s="9"/>
+        <v>14.057692307692308</v>
+      </c>
+      <c r="F109" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G109" s="11"/>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>7</v>
       </c>
-      <c r="B110" t="s">
-        <v>16</v>
+      <c r="B110" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D110" s="7">
-        <v>311</v>
+        <v>203</v>
       </c>
       <c r="E110" s="4">
-        <v>13.719230769232</v>
-      </c>
-      <c r="F110">
-        <v>33.26</v>
-      </c>
-      <c r="G110" s="9"/>
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F110" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G110" s="11"/>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>7</v>
       </c>
-      <c r="B111" t="s">
-        <v>16</v>
+      <c r="B111" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D111" s="7">
-        <v>312</v>
+        <v>249</v>
       </c>
       <c r="E111" s="4">
-        <v>13.740384615385899</v>
-      </c>
-      <c r="F111">
-        <v>33.369999999999997</v>
-      </c>
-      <c r="G111" s="9"/>
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F111" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G111" s="11"/>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>7</v>
       </c>
-      <c r="B112" t="s">
-        <v>16</v>
+      <c r="B112" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D112" s="7">
-        <v>1</v>
+        <v>301</v>
       </c>
       <c r="E112" s="4">
-        <v>13.7615384615398</v>
-      </c>
-      <c r="F112">
-        <v>33.479999999999997</v>
-      </c>
-      <c r="G112" s="8">
-        <v>1</v>
-      </c>
+        <v>13.423076923076923</v>
+      </c>
+      <c r="F112" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G112" s="10"/>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>7</v>
       </c>
-      <c r="B113" t="s">
-        <v>16</v>
+      <c r="B113" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D113" s="7">
-        <v>12</v>
+        <v>289</v>
       </c>
       <c r="E113" s="4">
-        <v>13.782692307693701</v>
-      </c>
-      <c r="F113">
-        <v>33.590000000000003</v>
-      </c>
-      <c r="G113" s="9"/>
+        <v>12.196153846153846</v>
+      </c>
+      <c r="F113" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G113" s="11"/>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>7</v>
       </c>
-      <c r="B114" t="s">
-        <v>16</v>
+      <c r="B114" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D114" s="7">
-        <v>24</v>
+        <v>248</v>
       </c>
       <c r="E114" s="4">
-        <v>13.8038461538476</v>
-      </c>
-      <c r="F114">
-        <v>33.700000000000003</v>
-      </c>
-      <c r="G114" s="9"/>
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F114" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G114" s="11"/>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>7</v>
       </c>
-      <c r="B115" t="s">
-        <v>16</v>
+      <c r="B115" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D115" s="7">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="E115" s="4">
-        <v>13.8250000000015</v>
-      </c>
-      <c r="F115">
-        <v>33.81</v>
-      </c>
-      <c r="G115" s="9"/>
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F115" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G115" s="11"/>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>7</v>
       </c>
-      <c r="B116" t="s">
-        <v>16</v>
+      <c r="B116" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D116" s="7">
-        <v>51</v>
+        <v>148</v>
       </c>
       <c r="E116" s="4">
-        <v>13.846153846155399</v>
-      </c>
-      <c r="F116">
-        <v>33.92</v>
-      </c>
-      <c r="G116" s="9"/>
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F116" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G116" s="11"/>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>7</v>
       </c>
-      <c r="B117" t="s">
-        <v>16</v>
+      <c r="B117" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D117" s="7">
-        <v>65</v>
+        <v>218</v>
       </c>
       <c r="E117" s="4">
-        <v>13.8673076923093</v>
-      </c>
-      <c r="F117">
-        <v>34.03</v>
-      </c>
-      <c r="G117" s="9"/>
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F117" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G117" s="11"/>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>7</v>
       </c>
-      <c r="B118" t="s">
-        <v>16</v>
+      <c r="B118" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D118" s="7">
-        <v>79</v>
+        <v>235</v>
       </c>
       <c r="E118" s="4">
-        <v>13.888461538463201</v>
-      </c>
-      <c r="F118">
-        <v>34.14</v>
-      </c>
-      <c r="G118" s="9"/>
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F118" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G118" s="11"/>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>7</v>
       </c>
-      <c r="B119" t="s">
-        <v>16</v>
+      <c r="B119" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D119" s="7">
-        <v>96</v>
+        <v>276</v>
       </c>
       <c r="E119" s="4">
-        <v>13.9096153846171</v>
-      </c>
-      <c r="F119">
-        <v>34.25</v>
-      </c>
-      <c r="G119" s="9"/>
+        <v>12.873076923076924</v>
+      </c>
+      <c r="F119" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G119" s="11"/>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>7</v>
       </c>
-      <c r="B120" t="s">
-        <v>16</v>
+      <c r="B120" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D120" s="7">
-        <v>111</v>
+        <v>262</v>
       </c>
       <c r="E120" s="4">
-        <v>13.930769230771</v>
-      </c>
-      <c r="F120">
-        <v>34.36</v>
-      </c>
-      <c r="G120" s="9"/>
+        <v>14.184615384615386</v>
+      </c>
+      <c r="F120" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G120" s="11"/>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>7</v>
       </c>
-      <c r="B121" t="s">
-        <v>16</v>
+      <c r="B121" s="7" t="s">
+        <v>15</v>
       </c>
       <c r="D121" s="7">
-        <v>129</v>
+        <v>303</v>
       </c>
       <c r="E121" s="4">
-        <v>13.951923076924899</v>
-      </c>
-      <c r="F121">
-        <v>34.47</v>
-      </c>
-      <c r="G121" s="9"/>
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F121" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="G121" s="11"/>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>7</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" s="7">
+        <v>304</v>
+      </c>
+      <c r="E122" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F122" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="G122" s="11"/>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A123" t="s">
+        <v>7</v>
+      </c>
+      <c r="B123" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" s="7">
+        <v>311</v>
+      </c>
+      <c r="E123" s="4">
+        <v>11.053846153846154</v>
+      </c>
+      <c r="F123" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="G123" s="10"/>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A124" t="s">
+        <v>7</v>
+      </c>
+      <c r="B124" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D124" s="7">
+        <v>302</v>
+      </c>
+      <c r="E124" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F124" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G124" s="11"/>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A125" t="s">
+        <v>7</v>
+      </c>
+      <c r="B125" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D125" s="7">
+        <v>302</v>
+      </c>
+      <c r="E125" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F125" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G125" s="11"/>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A126" t="s">
+        <v>7</v>
+      </c>
+      <c r="B126" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D126" s="7">
+        <v>310</v>
+      </c>
+      <c r="E126" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F126" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G126" s="11"/>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A127" t="s">
+        <v>7</v>
+      </c>
+      <c r="B127" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D127" s="7">
+        <v>305</v>
+      </c>
+      <c r="E127" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F127" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="G127" s="11"/>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A128" t="s">
+        <v>7</v>
+      </c>
+      <c r="B128" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" s="7">
+        <v>312</v>
+      </c>
+      <c r="E128" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F128" s="7">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G128" s="11"/>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A129" t="s">
+        <v>7</v>
+      </c>
+      <c r="B129" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D129" s="7">
+        <v>312</v>
+      </c>
+      <c r="E129" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F129" s="7">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G129" s="11"/>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A130" t="s">
+        <v>7</v>
+      </c>
+      <c r="B130" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D130" s="7">
+        <v>306</v>
+      </c>
+      <c r="E130" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F130" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="G130" s="11"/>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A131" t="s">
+        <v>7</v>
+      </c>
+      <c r="B131" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D131" s="7">
+        <v>307</v>
+      </c>
+      <c r="E131" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F131" s="7">
+        <v>33</v>
+      </c>
+      <c r="G131" s="11"/>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A132" t="s">
+        <v>7</v>
+      </c>
+      <c r="B132" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D132" s="7">
+        <v>308</v>
+      </c>
+      <c r="E132" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F132" s="7">
+        <v>33</v>
+      </c>
+      <c r="G132" s="11"/>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A133" t="s">
+        <v>7</v>
+      </c>
+      <c r="B133" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" s="7">
+        <v>309</v>
+      </c>
+      <c r="E133" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F133" s="7">
+        <v>33.9</v>
+      </c>
+      <c r="G133" s="11"/>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B134" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D134" s="7">
+        <v>23</v>
+      </c>
+      <c r="E134" s="4">
+        <v>11.265384615384615</v>
+      </c>
+      <c r="F134" s="7">
+        <v>28.5</v>
+      </c>
+      <c r="G134" s="10"/>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B135" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D135" s="7">
+        <v>10</v>
+      </c>
+      <c r="E135" s="4">
+        <v>14.015384615384615</v>
+      </c>
+      <c r="F135" s="7">
+        <v>28.7</v>
+      </c>
+      <c r="G135" s="11"/>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A136" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B136" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D136" s="7">
+        <v>36</v>
+      </c>
+      <c r="E136" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F136" s="7">
+        <v>28.8</v>
+      </c>
+      <c r="G136" s="11"/>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A137" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B137" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D137" s="7">
+        <v>11</v>
+      </c>
+      <c r="E137" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F137" s="7">
+        <v>29</v>
+      </c>
+      <c r="G137" s="11"/>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A138" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B138" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D138" s="7">
+        <v>11</v>
+      </c>
+      <c r="E138" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F138" s="7">
+        <v>29</v>
+      </c>
+      <c r="G138" s="11"/>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A139" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B139" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D139" s="7">
+        <v>9</v>
+      </c>
+      <c r="E139" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F139" s="7">
+        <v>29</v>
+      </c>
+      <c r="G139" s="11"/>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A140" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B140" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D140" s="7">
+        <v>50</v>
+      </c>
+      <c r="E140" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F140" s="7">
+        <v>29.2</v>
+      </c>
+      <c r="G140" s="11"/>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A141" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B141" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D141" s="7">
+        <v>8</v>
+      </c>
+      <c r="E141" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F141" s="7">
+        <v>29.4</v>
+      </c>
+      <c r="G141" s="11"/>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A142" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B142" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D142" s="7">
+        <v>64</v>
+      </c>
+      <c r="E142" s="4">
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F142" s="7">
+        <v>29.5</v>
+      </c>
+      <c r="G142" s="11"/>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A143" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B143" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D143" s="7">
+        <v>78</v>
+      </c>
+      <c r="E143" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F143" s="7">
+        <v>29.7</v>
+      </c>
+      <c r="G143" s="11"/>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A144" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B144" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D144" s="7">
+        <v>7</v>
+      </c>
+      <c r="E144" s="4">
+        <v>12.957692307692309</v>
+      </c>
+      <c r="F144" s="7">
+        <v>29.7</v>
+      </c>
+      <c r="G144" s="11"/>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A145" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B145" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D145" s="7">
+        <v>165</v>
+      </c>
+      <c r="E145" s="4">
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F145" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G145" s="10"/>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A146" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B146" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D146" s="7">
+        <v>147</v>
+      </c>
+      <c r="E146" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F146" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G146" s="11"/>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A147" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B147" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D147" s="7">
+        <v>128</v>
+      </c>
+      <c r="E147" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F147" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G147" s="11"/>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A148" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B148" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D148" s="7">
+        <v>95</v>
+      </c>
+      <c r="E148" s="4">
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F148" s="7">
+        <v>29.9</v>
+      </c>
+      <c r="G148" s="11"/>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B149" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D149" s="7">
+        <v>110</v>
+      </c>
+      <c r="E149" s="4">
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F149" s="7">
+        <v>30</v>
+      </c>
+      <c r="G149" s="11"/>
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B150" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D150" s="7">
+        <v>6</v>
+      </c>
+      <c r="E150" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F150" s="7">
+        <v>30</v>
+      </c>
+      <c r="G150" s="11"/>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A151" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B151" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D151" s="7">
+        <v>5</v>
+      </c>
+      <c r="E151" s="4">
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F151" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G151" s="11"/>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A152" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B152" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D152" s="7">
+        <v>4</v>
+      </c>
+      <c r="E152" s="4">
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F152" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G152" s="11"/>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A153" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B153" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D153" s="7">
+        <v>3</v>
+      </c>
+      <c r="E153" s="4">
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F153" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G153" s="11"/>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A154" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B154" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D154" s="7">
+        <v>2</v>
+      </c>
+      <c r="E154" s="4">
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F154" s="7">
+        <v>30.1</v>
+      </c>
+      <c r="G154" s="11"/>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A155" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D155" s="7">
+        <v>12</v>
+      </c>
+      <c r="E155" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F155" s="7">
+        <v>30.2</v>
+      </c>
+      <c r="G155" s="11"/>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A156" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B156" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D156" s="7">
+        <v>184</v>
+      </c>
+      <c r="E156" s="4">
+        <v>13.126923076923077</v>
+      </c>
+      <c r="F156" s="7">
+        <v>30.2</v>
+      </c>
+      <c r="G156" s="10"/>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A157" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B157" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D157" s="7">
+        <v>24</v>
+      </c>
+      <c r="E157" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F157" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="G157" s="11"/>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A158" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B158" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D158" s="7">
+        <v>165</v>
+      </c>
+      <c r="E158" s="4">
+        <v>13.592307692307692</v>
+      </c>
+      <c r="F158" s="7">
+        <v>30.5</v>
+      </c>
+      <c r="G158" s="11"/>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A159" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B159" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D159" s="7">
+        <v>1</v>
+      </c>
+      <c r="E159" s="4">
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F159" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G159" s="11"/>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A160" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B160" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D160" s="7">
+        <v>202</v>
+      </c>
+      <c r="E160" s="4">
+        <v>13.507692307692309</v>
+      </c>
+      <c r="F160" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G160" s="11"/>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A161" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B161" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D161" s="7">
+        <v>1</v>
+      </c>
+      <c r="E161" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F161" s="7">
+        <v>30.7</v>
+      </c>
+      <c r="G161" s="11"/>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A162" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B162" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D162" s="7">
+        <v>37</v>
+      </c>
+      <c r="E162" s="4">
+        <v>12.111538461538462</v>
+      </c>
+      <c r="F162" s="7">
+        <v>30.9</v>
+      </c>
+      <c r="G162" s="11"/>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A163" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D163" s="7">
+        <v>217</v>
+      </c>
+      <c r="E163" s="4">
+        <v>13.042307692307693</v>
+      </c>
+      <c r="F163" s="7">
+        <v>31.2</v>
+      </c>
+      <c r="G163" s="11"/>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A164" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B164" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D164" s="7">
+        <v>51</v>
+      </c>
+      <c r="E164" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F164" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G164" s="11"/>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A165" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B165" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D165" s="7">
+        <v>111</v>
+      </c>
+      <c r="E165" s="4">
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F165" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G165" s="11"/>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A166" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B166" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D166" s="7">
+        <v>129</v>
+      </c>
+      <c r="E166" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F166" s="7">
+        <v>31.3</v>
+      </c>
+      <c r="G166" s="11"/>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A167" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B167" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D167" s="7">
+        <v>166</v>
+      </c>
+      <c r="E167" s="4">
+        <v>14.226923076923077</v>
+      </c>
+      <c r="F167" s="7">
+        <v>31.4</v>
+      </c>
+      <c r="G167" s="10"/>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A168" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B168" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D168" s="7">
+        <v>65</v>
+      </c>
+      <c r="E168" s="4">
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F168" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G168" s="11"/>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A169" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B169" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D169" s="7">
+        <v>96</v>
+      </c>
+      <c r="E169" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F169" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G169" s="11"/>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A170" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B170" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D170" s="7">
+        <v>185</v>
+      </c>
+      <c r="E170" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F170" s="7">
+        <v>31.5</v>
+      </c>
+      <c r="G170" s="11"/>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A171" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B171" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D171" s="7">
+        <v>79</v>
+      </c>
+      <c r="E171" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F171" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G171" s="11"/>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A172" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B172" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D172" s="7">
+        <v>263</v>
+      </c>
+      <c r="E172" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F172" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G172" s="11"/>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A173" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B173" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D173" s="7">
+        <v>277</v>
+      </c>
+      <c r="E173" s="4">
+        <v>11.9</v>
+      </c>
+      <c r="F173" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G173" s="11"/>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A174" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B174" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D174" s="7">
+        <v>290</v>
+      </c>
+      <c r="E174" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F174" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G174" s="11"/>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A175" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B175" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D175" s="7">
+        <v>234</v>
+      </c>
+      <c r="E175" s="4">
+        <v>14.057692307692308</v>
+      </c>
+      <c r="F175" s="7">
+        <v>31.6</v>
+      </c>
+      <c r="G175" s="11"/>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A176" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B176" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D176" s="7">
+        <v>203</v>
+      </c>
+      <c r="E176" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F176" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G176" s="11"/>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A177" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B177" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D177" s="7">
+        <v>249</v>
+      </c>
+      <c r="E177" s="4">
+        <v>13.803846153846155</v>
+      </c>
+      <c r="F177" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G177" s="11"/>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A178" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B178" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D178" s="7">
+        <v>301</v>
+      </c>
+      <c r="E178" s="4">
+        <v>13.423076923076923</v>
+      </c>
+      <c r="F178" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G178" s="10"/>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A179" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B179" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D179" s="7">
+        <v>289</v>
+      </c>
+      <c r="E179" s="4">
+        <v>12.196153846153846</v>
+      </c>
+      <c r="F179" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G179" s="11"/>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A180" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B180" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D180" s="7">
+        <v>248</v>
+      </c>
+      <c r="E180" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F180" s="7">
+        <v>31.8</v>
+      </c>
+      <c r="G180" s="11"/>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B181" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D181" s="7">
+        <v>148</v>
+      </c>
+      <c r="E181" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F181" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G181" s="11"/>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B182" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D182" s="7">
+        <v>148</v>
+      </c>
+      <c r="E182" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F182" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G182" s="11"/>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A183" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B183" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D183" s="7">
+        <v>218</v>
+      </c>
+      <c r="E183" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F183" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G183" s="11"/>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A184" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B184" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D184" s="7">
+        <v>235</v>
+      </c>
+      <c r="E184" s="4">
+        <v>13.16923076923077</v>
+      </c>
+      <c r="F184" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G184" s="11"/>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A185" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B185" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D185" s="7">
+        <v>276</v>
+      </c>
+      <c r="E185" s="4">
+        <v>12.873076923076924</v>
+      </c>
+      <c r="F185" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G185" s="11"/>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A186" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B186" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D186" s="7">
+        <v>262</v>
+      </c>
+      <c r="E186" s="4">
+        <v>14.184615384615386</v>
+      </c>
+      <c r="F186" s="7">
+        <v>31.9</v>
+      </c>
+      <c r="G186" s="11"/>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A187" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B187" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D187" s="7">
+        <v>303</v>
+      </c>
+      <c r="E187" s="4">
+        <v>11.688461538461539</v>
+      </c>
+      <c r="F187" s="7">
+        <v>32.1</v>
+      </c>
+      <c r="G187" s="11"/>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A188" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B188" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D188" s="7">
+        <v>304</v>
+      </c>
+      <c r="E188" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F188" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="G188" s="11"/>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A189" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B189" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D189" s="7">
+        <v>311</v>
+      </c>
+      <c r="E189" s="4">
+        <v>11.053846153846154</v>
+      </c>
+      <c r="F189" s="7">
+        <v>32.4</v>
+      </c>
+      <c r="G189" s="10"/>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A190" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B190" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D190" s="7">
+        <v>302</v>
+      </c>
+      <c r="E190" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F190" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G190" s="11"/>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A191" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B191" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D191" s="7">
+        <v>302</v>
+      </c>
+      <c r="E191" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F191" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G191" s="11"/>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A192" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B192" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D192" s="7">
+        <v>310</v>
+      </c>
+      <c r="E192" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F192" s="7">
+        <v>32.6</v>
+      </c>
+      <c r="G192" s="11"/>
+    </row>
+    <row r="193" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A193" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B193" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D193" s="7">
+        <v>305</v>
+      </c>
+      <c r="E193" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F193" s="7">
+        <v>32.700000000000003</v>
+      </c>
+      <c r="G193" s="11"/>
+    </row>
+    <row r="194" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A194" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B194" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D194" s="7">
+        <v>312</v>
+      </c>
+      <c r="E194" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F194" s="7">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G194" s="11"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A195" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B195" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D195" s="7">
+        <v>312</v>
+      </c>
+      <c r="E195" s="4">
+        <v>12.746153846153847</v>
+      </c>
+      <c r="F195" s="7">
+        <v>32.799999999999997</v>
+      </c>
+      <c r="G195" s="11"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A196" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B196" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D196" s="7">
+        <v>306</v>
+      </c>
+      <c r="E196" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F196" s="7">
+        <v>32.9</v>
+      </c>
+      <c r="G196" s="11"/>
+    </row>
+    <row r="197" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A197" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B197" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D197" s="7">
+        <v>307</v>
+      </c>
+      <c r="E197" s="4">
+        <v>13.380769230769232</v>
+      </c>
+      <c r="F197" s="7">
+        <v>33</v>
+      </c>
+      <c r="G197" s="11"/>
+    </row>
+    <row r="198" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A198" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B198" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D198" s="7">
+        <v>308</v>
+      </c>
+      <c r="E198" s="4">
+        <v>12.534615384615385</v>
+      </c>
+      <c r="F198" s="7">
+        <v>33</v>
+      </c>
+      <c r="G198" s="11"/>
+    </row>
+    <row r="199" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A199" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="B199" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="D199" s="7">
+        <v>309</v>
+      </c>
+      <c r="E199" s="4">
+        <v>12.323076923076924</v>
+      </c>
+      <c r="F199" s="7">
+        <v>33.9</v>
+      </c>
+      <c r="G199" s="11"/>
+    </row>
+    <row r="200" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A200" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B200" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7">
+        <v>249</v>
+      </c>
+      <c r="E200" s="4">
+        <v>13.467199999999998</v>
+      </c>
+      <c r="F200" s="7">
+        <v>36</v>
+      </c>
+      <c r="G200" s="8"/>
+    </row>
+    <row r="201" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A201" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B201" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C201" s="7"/>
+      <c r="D201" s="7">
+        <v>263</v>
+      </c>
+      <c r="E201" s="4">
+        <v>10.414900000000005</v>
+      </c>
+      <c r="F201" s="7">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A202" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B202" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C202" s="7"/>
+      <c r="D202" s="7">
+        <v>277</v>
+      </c>
+      <c r="E202" s="4">
+        <v>13.236699999999999</v>
+      </c>
+      <c r="F202" s="7">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A203" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B203" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C203" s="7"/>
+      <c r="D203" s="7">
+        <v>290</v>
+      </c>
+      <c r="E203" s="4">
+        <v>11.889699999999998</v>
+      </c>
+      <c r="F203" s="7">
+        <v>36.5</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A204" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B204" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C204" s="7"/>
+      <c r="D204" s="7">
+        <v>302</v>
+      </c>
+      <c r="E204" s="4">
+        <v>12.406099999999995</v>
+      </c>
+      <c r="F204" s="7">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A205" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B205" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C205" s="7"/>
+      <c r="D205" s="7">
+        <v>303</v>
+      </c>
+      <c r="E205" s="4">
+        <v>12</v>
+      </c>
+      <c r="F205" s="7">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A206" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B206" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C206" s="7"/>
+      <c r="D206" s="7">
+        <v>304</v>
+      </c>
+      <c r="E206" s="4">
+        <v>13.480300000000002</v>
+      </c>
+      <c r="F206" s="7">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A207" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B207" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C207" s="7"/>
+      <c r="D207" s="7">
+        <v>305</v>
+      </c>
+      <c r="E207" s="4">
+        <v>13.480300000000002</v>
+      </c>
+      <c r="F207" s="7">
+        <v>37.200000000000003</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A208" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B208" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C208" s="7"/>
+      <c r="D208" s="7">
+        <v>302</v>
+      </c>
+      <c r="E208" s="4">
+        <v>12.102974999999995</v>
+      </c>
+      <c r="F208" s="7">
+        <v>37.299999999999997</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A209" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B209" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C209" s="7"/>
+      <c r="D209" s="7">
+        <v>13</v>
+      </c>
+      <c r="E209" s="4">
+        <v>14</v>
+      </c>
+      <c r="F209" s="7">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A210" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B210" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C210" s="7"/>
+      <c r="D210" s="7">
+        <v>13</v>
+      </c>
+      <c r="E210" s="4">
+        <v>11.593899999999998</v>
+      </c>
+      <c r="F210" s="7">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A211" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B211" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7">
+        <v>1</v>
+      </c>
+      <c r="E211" s="4">
+        <v>9.733700000000006</v>
+      </c>
+      <c r="F211" s="7">
+        <v>37.4</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A212" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B212" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C212" s="7"/>
+      <c r="D212" s="7">
+        <v>1</v>
+      </c>
+      <c r="E212" s="4">
+        <v>11.777449999999998</v>
+      </c>
+      <c r="F212" s="7">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A213" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B213" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C213" s="7"/>
+      <c r="D213" s="7">
+        <v>25</v>
+      </c>
+      <c r="E213" s="4">
+        <v>11.777449999999998</v>
+      </c>
+      <c r="F213" s="7">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A214" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B214" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C214" s="7"/>
+      <c r="D214" s="7">
+        <v>38</v>
+      </c>
+      <c r="E214" s="4">
+        <v>12.417274999999997</v>
+      </c>
+      <c r="F214" s="7">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A215" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B215" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C215" s="7"/>
+      <c r="D215" s="7">
+        <v>149</v>
+      </c>
+      <c r="E215" s="4">
+        <v>12.497800000000002</v>
+      </c>
+      <c r="F215" s="7">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A216" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B216" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C216" s="7"/>
+      <c r="D216" s="7">
+        <v>149</v>
+      </c>
+      <c r="E216" s="4">
+        <v>9.8384999999999998</v>
+      </c>
+      <c r="F216" s="7">
+        <v>37.700000000000003</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A217" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B217" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C217" s="7"/>
+      <c r="D217" s="7">
+        <v>12</v>
+      </c>
+      <c r="E217" s="4">
+        <v>12.746699999999999</v>
+      </c>
+      <c r="F217" s="7">
+        <v>37.799999999999997</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A218" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B218" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C218" s="7"/>
+      <c r="D218" s="7">
+        <v>24</v>
+      </c>
+      <c r="E218" s="4">
+        <v>10.946800000000001</v>
+      </c>
+      <c r="F218" s="7">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A219" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B219" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C219" s="7"/>
+      <c r="D219" s="7">
+        <v>52</v>
+      </c>
+      <c r="E219" s="4">
+        <v>11.306000000000001</v>
+      </c>
+      <c r="F219" s="7">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A220" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B220" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7">
+        <v>14</v>
+      </c>
+      <c r="E220" s="4">
+        <v>11.947599999999996</v>
+      </c>
+      <c r="F220" s="7">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A221" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B221" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C221" s="7"/>
+      <c r="D221" s="7">
+        <v>148</v>
+      </c>
+      <c r="E221" s="4">
+        <v>11.410500000000001</v>
+      </c>
+      <c r="F221" s="7">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A222" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B222" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C222" s="7"/>
+      <c r="D222" s="7">
+        <v>148</v>
+      </c>
+      <c r="E222" s="4">
+        <v>11.609074999999999</v>
+      </c>
+      <c r="F222" s="7">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A223" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B223" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C223" s="7"/>
+      <c r="D223" s="7">
+        <v>37</v>
+      </c>
+      <c r="E223" s="4">
+        <v>12.445399999999998</v>
+      </c>
+      <c r="F223" s="7">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A224" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B224" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C224" s="7"/>
+      <c r="D224" s="7">
+        <v>66</v>
+      </c>
+      <c r="E224" s="4">
+        <v>12.406100000000002</v>
+      </c>
+      <c r="F224" s="7">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="225" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A225" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B225" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C225" s="7"/>
+      <c r="D225" s="7">
+        <v>15</v>
+      </c>
+      <c r="E225" s="4">
+        <v>12.406100000000002</v>
+      </c>
+      <c r="F225" s="7">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="226" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A226" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B226" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C226" s="7"/>
+      <c r="D226" s="7">
+        <v>80</v>
+      </c>
+      <c r="E226" s="4">
+        <v>9.8123000000000005</v>
+      </c>
+      <c r="F226" s="7">
+        <v>38.1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A227" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B227" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C227" s="7"/>
+      <c r="D227" s="7">
+        <v>51</v>
+      </c>
+      <c r="E227" s="4">
+        <v>11.822349999999997</v>
+      </c>
+      <c r="F227" s="7">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="228" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A228" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C228" s="7"/>
+      <c r="D228" s="7">
+        <v>2</v>
+      </c>
+      <c r="E228" s="4">
+        <v>11.249874999999999</v>
+      </c>
+      <c r="F228" s="7">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="229" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A229" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C229" s="7"/>
+      <c r="D229" s="7">
+        <v>97</v>
+      </c>
+      <c r="E229" s="4">
+        <v>12.361149999999997</v>
+      </c>
+      <c r="F229" s="7">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="230" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A230" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B230" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C230" s="7"/>
+      <c r="D230" s="7">
+        <v>112</v>
+      </c>
+      <c r="E230" s="4">
+        <v>11.957050000000001</v>
+      </c>
+      <c r="F230" s="7">
+        <v>38.299999999999997</v>
+      </c>
+    </row>
+    <row r="231" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A231" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C231" s="7"/>
+      <c r="D231" s="7">
+        <v>65</v>
+      </c>
+      <c r="E231" s="4">
+        <v>11.788675000000001</v>
+      </c>
+      <c r="F231" s="7">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A232" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B232" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C232" s="7"/>
+      <c r="D232" s="7">
+        <v>130</v>
+      </c>
+      <c r="E232" s="4">
+        <v>10.179100000000004</v>
+      </c>
+      <c r="F232" s="7">
+        <v>38.4</v>
+      </c>
+    </row>
+    <row r="233" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A233" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B233" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7">
+        <v>22</v>
+      </c>
+      <c r="E233" s="4">
+        <v>13.362400000000004</v>
+      </c>
+      <c r="F233" s="7">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="234" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A234" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B234" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C234" s="7"/>
+      <c r="D234" s="7">
+        <v>22</v>
+      </c>
+      <c r="E234" s="4">
+        <v>9.8909000000000038</v>
+      </c>
+      <c r="F234" s="7">
+        <v>38.700000000000003</v>
+      </c>
+    </row>
+    <row r="235" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A235" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B235" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C235" s="7"/>
+      <c r="D235" s="7">
         <v>16</v>
       </c>
-      <c r="D122" s="7">
-        <v>148</v>
-      </c>
-      <c r="E122" s="4">
-        <v>13.9730769230788</v>
-      </c>
-      <c r="F122">
-        <v>34.58</v>
-      </c>
-      <c r="G122" s="9"/>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A123" s="7" t="s">
+      <c r="E235" s="4">
+        <v>13.910199999999998</v>
+      </c>
+      <c r="F235" s="7">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="236" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A236" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B236" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C236" s="7"/>
+      <c r="D236" s="7">
+        <v>79</v>
+      </c>
+      <c r="E236" s="4">
+        <v>13.910199999999998</v>
+      </c>
+      <c r="F236" s="7">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="237" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A237" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B237" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C237" s="7"/>
+      <c r="D237" s="7">
+        <v>96</v>
+      </c>
+      <c r="E237" s="4">
+        <v>9.9957000000000065</v>
+      </c>
+      <c r="F237" s="7">
+        <v>38.799999999999997</v>
+      </c>
+    </row>
+    <row r="238" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A238" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B238" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C238" s="7"/>
+      <c r="D238" s="7">
+        <v>111</v>
+      </c>
+      <c r="E238" s="4">
+        <v>12.720349999999996</v>
+      </c>
+      <c r="F238" s="7">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A239" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B239" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C239" s="7"/>
+      <c r="D239" s="7">
+        <v>3</v>
+      </c>
+      <c r="E239" s="4">
+        <v>9.4454999999999991</v>
+      </c>
+      <c r="F239" s="7">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="240" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A240" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B240" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C240" s="7"/>
+      <c r="D240" s="7">
+        <v>129</v>
+      </c>
+      <c r="E240" s="4">
+        <v>10.336300000000001</v>
+      </c>
+      <c r="F240" s="7">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="241" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A241" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B241" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C241" s="7"/>
+      <c r="D241" s="7">
+        <v>17</v>
+      </c>
+      <c r="E241" s="4">
+        <v>12.798925000000001</v>
+      </c>
+      <c r="F241" s="7">
+        <v>39.1</v>
+      </c>
+    </row>
+    <row r="242" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A242" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B242" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C242" s="7"/>
+      <c r="D242" s="7">
+        <v>167</v>
+      </c>
+      <c r="E242" s="4">
+        <v>12.136649999999998</v>
+      </c>
+      <c r="F242" s="7">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="243" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A243" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B243" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C243" s="7"/>
+      <c r="D243" s="7">
+        <v>18</v>
+      </c>
+      <c r="E243" s="4">
+        <v>12.327500000000001</v>
+      </c>
+      <c r="F243" s="7">
+        <v>39.299999999999997</v>
+      </c>
+    </row>
+    <row r="244" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A244" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B244" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C244" s="7"/>
+      <c r="D244" s="7">
+        <v>11</v>
+      </c>
+      <c r="E244" s="4">
+        <v>11.0175</v>
+      </c>
+      <c r="F244" s="7">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="245" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A245" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B245" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C245" s="7"/>
+      <c r="D245" s="7">
+        <v>11</v>
+      </c>
+      <c r="E245" s="4">
+        <v>11.842800000000002</v>
+      </c>
+      <c r="F245" s="7">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="246" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A246" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B246" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C246" s="7"/>
+      <c r="D246" s="7">
+        <v>19</v>
+      </c>
+      <c r="E246" s="4">
+        <v>11.842800000000002</v>
+      </c>
+      <c r="F246" s="7">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="247" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A247" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B247" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C247" s="7"/>
+      <c r="D247" s="7">
+        <v>4</v>
+      </c>
+      <c r="E247" s="4">
+        <v>10.8734</v>
+      </c>
+      <c r="F247" s="7">
+        <v>39.4</v>
+      </c>
+    </row>
+    <row r="248" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A248" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B248" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C248" s="7"/>
+      <c r="D248" s="7">
+        <v>20</v>
+      </c>
+      <c r="E248" s="4">
+        <v>12.226449999999998</v>
+      </c>
+      <c r="F248" s="7">
+        <v>39.5</v>
+      </c>
+    </row>
+    <row r="249" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A249" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B249" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C249" s="7"/>
+      <c r="D249" s="7">
+        <v>21</v>
+      </c>
+      <c r="E249" s="4">
+        <v>11.0175</v>
+      </c>
+      <c r="F249" s="7">
+        <v>39.6</v>
+      </c>
+    </row>
+    <row r="250" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A250" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B250" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C250" s="7"/>
+      <c r="D250" s="7">
+        <v>166</v>
+      </c>
+      <c r="E250" s="4">
+        <v>12.361149999999997</v>
+      </c>
+      <c r="F250" s="7">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="251" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A251" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B251" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C251" s="7"/>
+      <c r="D251" s="7">
+        <v>5</v>
+      </c>
+      <c r="E251" s="4">
+        <v>12.4285</v>
+      </c>
+      <c r="F251" s="7">
+        <v>39.700000000000003</v>
+      </c>
+    </row>
+    <row r="252" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A252" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B252" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C252" s="7"/>
+      <c r="D252" s="7">
+        <v>186</v>
+      </c>
+      <c r="E252" s="4">
+        <v>13.057099999999997</v>
+      </c>
+      <c r="F252" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="253" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A253" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B253" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C253" s="7"/>
+      <c r="D253" s="7">
+        <v>300</v>
+      </c>
+      <c r="E253" s="4">
+        <v>12.518300000000002</v>
+      </c>
+      <c r="F253" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="254" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A254" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B254" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C254" s="7"/>
+      <c r="D254" s="7">
+        <v>164</v>
+      </c>
+      <c r="E254" s="4">
+        <v>13.519600000000002</v>
+      </c>
+      <c r="F254" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="255" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A255" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B255" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C255" s="7"/>
+      <c r="D255" s="7">
+        <v>164</v>
+      </c>
+      <c r="E255" s="4">
+        <v>12.943199999999999</v>
+      </c>
+      <c r="F255" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="256" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A256" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B256" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C256" s="7"/>
+      <c r="D256" s="7">
+        <v>35</v>
+      </c>
+      <c r="E256" s="4">
+        <v>12.943199999999999</v>
+      </c>
+      <c r="F256" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="257" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A257" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B257" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C257" s="7"/>
+      <c r="D257" s="7">
+        <v>6</v>
+      </c>
+      <c r="E257" s="4">
+        <v>9.471700000000002</v>
+      </c>
+      <c r="F257" s="7">
+        <v>39.799999999999997</v>
+      </c>
+    </row>
+    <row r="258" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A258" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B258" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C258" s="7"/>
+      <c r="D258" s="7">
+        <v>300</v>
+      </c>
+      <c r="E258" s="4">
+        <v>11.575399999999998</v>
+      </c>
+      <c r="F258" s="7">
+        <v>39.9</v>
+      </c>
+    </row>
+    <row r="259" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A259" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B259" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C259" s="7"/>
+      <c r="D259" s="7">
+        <v>185</v>
+      </c>
+      <c r="E259" s="4">
+        <v>13.685699999999999</v>
+      </c>
+      <c r="F259" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="260" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A260" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B260" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C260" s="7"/>
+      <c r="D260" s="7">
         <v>7</v>
       </c>
-      <c r="B123" s="7" t="s">
+      <c r="E260" s="4">
+        <v>13.685699999999999</v>
+      </c>
+      <c r="F260" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="261" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A261" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B261" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C123" s="7"/>
-      <c r="D123" s="7">
-        <v>1</v>
-      </c>
-      <c r="E123" s="4">
-        <v>8.7307692307692299</v>
-      </c>
-      <c r="F123" s="7">
-        <v>22.4</v>
-      </c>
-      <c r="G123" s="8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A124" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B124" s="7" t="s">
+      <c r="C261" s="7"/>
+      <c r="D261" s="7">
+        <v>9</v>
+      </c>
+      <c r="E261" s="4">
+        <v>14.089799999999999</v>
+      </c>
+      <c r="F261" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A262" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B262" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C124" s="7"/>
-      <c r="D124" s="7">
-        <v>12</v>
-      </c>
-      <c r="E124" s="4">
-        <v>9.1538461538461533</v>
-      </c>
-      <c r="F124" s="7">
-        <v>22.4</v>
-      </c>
-      <c r="G124" s="9"/>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A125" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B125" s="7" t="s">
+      <c r="C262" s="7"/>
+      <c r="D262" s="7">
+        <v>8</v>
+      </c>
+      <c r="E262" s="4">
+        <v>12.372375</v>
+      </c>
+      <c r="F262" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A263" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B263" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C125" s="7"/>
-      <c r="D125" s="7">
-        <v>24</v>
-      </c>
-      <c r="E125" s="4">
-        <v>9.7884615384615383</v>
-      </c>
-      <c r="F125" s="7">
-        <v>22.6</v>
-      </c>
-      <c r="G125" s="9"/>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A126" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B126" s="7" t="s">
+      <c r="C263" s="7"/>
+      <c r="D263" s="7">
+        <v>204</v>
+      </c>
+      <c r="E263" s="4">
+        <v>8.9870000000000001</v>
+      </c>
+      <c r="F263" s="7">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A264" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B264" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C126" s="7"/>
-      <c r="D126" s="7">
-        <v>37</v>
-      </c>
-      <c r="E126" s="4">
-        <v>10.42307692307692</v>
-      </c>
-      <c r="F126" s="7">
-        <v>22.6</v>
-      </c>
-      <c r="G126" s="9"/>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A127" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B127" s="7" t="s">
+      <c r="C264" s="7"/>
+      <c r="D264" s="7">
+        <v>291</v>
+      </c>
+      <c r="E264" s="4">
+        <v>12.226449999999998</v>
+      </c>
+      <c r="F264" s="7">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A265" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B265" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C127" s="7"/>
-      <c r="D127" s="7">
-        <v>51</v>
-      </c>
-      <c r="E127" s="4">
-        <v>10.42307692307692</v>
-      </c>
-      <c r="F127" s="7">
-        <v>22.7</v>
-      </c>
-      <c r="G127" s="9"/>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A128" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B128" s="7" t="s">
+      <c r="C265" s="7"/>
+      <c r="D265" s="7">
+        <v>291</v>
+      </c>
+      <c r="E265" s="4">
+        <v>12.226449999999998</v>
+      </c>
+      <c r="F265" s="7">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A266" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B266" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C128" s="7"/>
-      <c r="D128" s="7">
-        <v>65</v>
-      </c>
-      <c r="E128" s="4">
-        <v>8.5192307692307701</v>
-      </c>
-      <c r="F128" s="7">
-        <v>22.7</v>
-      </c>
-      <c r="G128" s="9"/>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A129" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B129" s="7" t="s">
+      <c r="C266" s="7"/>
+      <c r="D266" s="7">
+        <v>49</v>
+      </c>
+      <c r="E266" s="4">
+        <v>13.270699999999998</v>
+      </c>
+      <c r="F266" s="7">
+        <v>40.299999999999997</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A267" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B267" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C129" s="7"/>
-      <c r="D129" s="7">
-        <v>79</v>
-      </c>
-      <c r="E129" s="4">
-        <v>10.21153846153846</v>
-      </c>
-      <c r="F129" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="G129" s="9"/>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A130" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B130" s="7" t="s">
+      <c r="C267" s="7"/>
+      <c r="D267" s="7">
+        <v>10</v>
+      </c>
+      <c r="E267" s="4">
+        <v>12.035625</v>
+      </c>
+      <c r="F267" s="7">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A268" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B268" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C130" s="7"/>
-      <c r="D130" s="7">
-        <v>96</v>
-      </c>
-      <c r="E130" s="4">
-        <v>8.5192307692307701</v>
-      </c>
-      <c r="F130" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="G130" s="9"/>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A131" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B131" s="7" t="s">
+      <c r="C268" s="7"/>
+      <c r="D268" s="7">
+        <v>165</v>
+      </c>
+      <c r="E268" s="4">
+        <v>10.703100000000003</v>
+      </c>
+      <c r="F268" s="7">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A269" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B269" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C131" s="7"/>
-      <c r="D131" s="7">
-        <v>111</v>
-      </c>
-      <c r="E131" s="4">
-        <v>10.63461538461539</v>
-      </c>
-      <c r="F131" s="7">
-        <v>22.8</v>
-      </c>
-      <c r="G131" s="9"/>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A132" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B132" s="7" t="s">
+      <c r="C269" s="7"/>
+      <c r="D269" s="7">
+        <v>165</v>
+      </c>
+      <c r="E269" s="4">
+        <v>10.349399999999997</v>
+      </c>
+      <c r="F269" s="7">
+        <v>40.5</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A270" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B270" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C132" s="7"/>
-      <c r="D132" s="7">
-        <v>129</v>
-      </c>
-      <c r="E132" s="4">
-        <v>9.365384615384615</v>
-      </c>
-      <c r="F132" s="7">
+      <c r="C270" s="7"/>
+      <c r="D270" s="7">
+        <v>36</v>
+      </c>
+      <c r="E270" s="4">
+        <v>13.348949999999999</v>
+      </c>
+      <c r="F270" s="7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A271" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B271" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C271" s="7"/>
+      <c r="D271" s="7">
         <v>23</v>
       </c>
-      <c r="G132" s="9"/>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A133" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B133" s="7" t="s">
+      <c r="E271" s="4">
+        <v>13.348949999999999</v>
+      </c>
+      <c r="F271" s="7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A272" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B272" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="C133" s="7"/>
-      <c r="D133" s="7">
-        <v>148</v>
-      </c>
-      <c r="E133" s="4">
-        <v>9.365384615384615</v>
-      </c>
-      <c r="F133" s="7">
-        <v>23</v>
-      </c>
-      <c r="G133" s="9"/>
+      <c r="C272" s="7"/>
+      <c r="D272" s="7">
+        <v>63</v>
+      </c>
+      <c r="E272" s="4">
+        <v>12.497800000000002</v>
+      </c>
+      <c r="F272" s="7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A273" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C273" s="9"/>
+      <c r="D273" s="7">
+        <v>312</v>
+      </c>
+      <c r="E273" s="4">
+        <v>10.7555</v>
+      </c>
+      <c r="F273" s="7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A274" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C274" s="7"/>
+      <c r="D274" s="7">
+        <v>312</v>
+      </c>
+      <c r="E274" s="4">
+        <v>10.336300000000001</v>
+      </c>
+      <c r="F274" s="7">
+        <v>40.6</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A275" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B275" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C275" s="7"/>
+      <c r="D275" s="7">
+        <v>219</v>
+      </c>
+      <c r="E275" s="4">
+        <v>11.109199999999998</v>
+      </c>
+      <c r="F275" s="7">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A276" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B276" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C276" s="7"/>
+      <c r="D276" s="7">
+        <v>203</v>
+      </c>
+      <c r="E276" s="4">
+        <v>10.388699999999998</v>
+      </c>
+      <c r="F276" s="7">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A277" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B277" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C277" s="7"/>
+      <c r="D277" s="7">
+        <v>183</v>
+      </c>
+      <c r="E277" s="4">
+        <v>10.454200000000002</v>
+      </c>
+      <c r="F277" s="7">
+        <v>40.700000000000003</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A278" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B278" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C278" s="7"/>
+      <c r="D278" s="7">
+        <v>201</v>
+      </c>
+      <c r="E278" s="4">
+        <v>13.898975</v>
+      </c>
+      <c r="F278" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A279" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B279" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C279" s="7"/>
+      <c r="D279" s="7">
+        <v>302</v>
+      </c>
+      <c r="E279" s="4">
+        <v>11.724900000000005</v>
+      </c>
+      <c r="F279" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A280" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B280" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C280" s="7"/>
+      <c r="D280" s="7">
+        <v>302</v>
+      </c>
+      <c r="E280" s="4">
+        <v>11.214</v>
+      </c>
+      <c r="F280" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A281" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B281" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C281" s="7"/>
+      <c r="D281" s="7">
+        <v>236</v>
+      </c>
+      <c r="E281" s="4">
+        <v>10.545899999999996</v>
+      </c>
+      <c r="F281" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A282" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B282" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C282" s="7"/>
+      <c r="D282" s="7">
+        <v>147</v>
+      </c>
+      <c r="E282" s="4">
+        <v>10.899600000000003</v>
+      </c>
+      <c r="F282" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A283" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B283" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C283" s="7"/>
+      <c r="D283" s="7">
+        <v>77</v>
+      </c>
+      <c r="E283" s="4">
+        <v>10.467300000000002</v>
+      </c>
+      <c r="F283" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A284" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B284" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C284" s="7"/>
+      <c r="D284" s="7">
+        <v>288</v>
+      </c>
+      <c r="E284" s="4">
+        <v>10.428000000000001</v>
+      </c>
+      <c r="F284" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A285" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B285" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C285" s="7"/>
+      <c r="D285" s="7">
+        <v>213</v>
+      </c>
+      <c r="E285" s="4">
+        <v>10.113600000000003</v>
+      </c>
+      <c r="F285" s="7">
+        <v>40.799999999999997</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A286" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B286" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C286" s="7"/>
+      <c r="D286" s="7">
+        <v>127</v>
+      </c>
+      <c r="E286" s="4">
+        <v>12.271349999999996</v>
+      </c>
+      <c r="F286" s="7">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A287" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B287" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C287" s="7"/>
+      <c r="D287" s="7">
+        <v>50</v>
+      </c>
+      <c r="E287" s="4">
+        <v>12.930100000000003</v>
+      </c>
+      <c r="F287" s="7">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A288" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B288" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C288" s="7"/>
+      <c r="D288" s="7">
+        <v>250</v>
+      </c>
+      <c r="E288" s="4">
+        <v>10.663800000000002</v>
+      </c>
+      <c r="F288" s="7">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A289" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B289" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C289" s="7"/>
+      <c r="D289" s="7">
+        <v>264</v>
+      </c>
+      <c r="E289" s="4">
+        <v>11.200900000000001</v>
+      </c>
+      <c r="F289" s="7">
+        <v>40.9</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A290" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B290" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C290" s="7"/>
+      <c r="D290" s="7">
+        <v>275</v>
+      </c>
+      <c r="E290" s="4">
+        <v>12.248899999999997</v>
+      </c>
+      <c r="F290" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A291" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B291" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C291" s="7"/>
+      <c r="D291" s="7">
+        <v>261</v>
+      </c>
+      <c r="E291" s="4">
+        <v>13.977550000000001</v>
+      </c>
+      <c r="F291" s="7">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A292" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B292" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C292" s="7"/>
+      <c r="D292" s="7">
+        <v>247</v>
+      </c>
+      <c r="E292" s="4">
+        <v>12.147874999999999</v>
+      </c>
+      <c r="F292" s="7">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A293" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B293" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C293" s="7"/>
+      <c r="D293" s="7">
+        <v>233</v>
+      </c>
+      <c r="E293" s="4">
+        <v>11.620099999999995</v>
+      </c>
+      <c r="F293" s="7">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A294" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B294" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C294" s="7"/>
+      <c r="D294" s="7">
+        <v>94</v>
+      </c>
+      <c r="E294" s="4">
+        <v>13.595899999999997</v>
+      </c>
+      <c r="F294" s="7">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A295" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B295" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C295" s="7"/>
+      <c r="D295" s="7">
+        <v>218</v>
+      </c>
+      <c r="E295" s="4">
+        <v>12.078599999999996</v>
+      </c>
+      <c r="F295" s="7">
+        <v>41.2</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A296" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B296" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C296" s="7"/>
+      <c r="D296" s="7">
+        <v>278</v>
+      </c>
+      <c r="E296" s="4">
+        <v>11.945824999999999</v>
+      </c>
+      <c r="F296" s="7">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A297" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B297" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C297" s="7"/>
+      <c r="D297" s="7">
+        <v>299</v>
+      </c>
+      <c r="E297" s="4">
+        <v>12.608099999999997</v>
+      </c>
+      <c r="F297" s="7">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A298" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B298" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C298" s="7"/>
+      <c r="D298" s="7">
+        <v>109</v>
+      </c>
+      <c r="E298" s="4">
+        <v>13.988774999999997</v>
+      </c>
+      <c r="F298" s="7">
+        <v>41.3</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A299" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B299" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C299" s="7"/>
+      <c r="D299" s="7">
+        <v>292</v>
+      </c>
+      <c r="E299" s="4">
+        <v>12.305024999999997</v>
+      </c>
+      <c r="F299" s="7">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A300" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B300" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C300" s="7"/>
+      <c r="D300" s="7">
+        <v>202</v>
+      </c>
+      <c r="E300" s="4">
+        <v>13.113224999999996</v>
+      </c>
+      <c r="F300" s="7">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A301" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B301" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C301" s="7"/>
+      <c r="D301" s="7">
+        <v>184</v>
+      </c>
+      <c r="E301" s="4">
+        <v>14.29185</v>
+      </c>
+      <c r="F301" s="7">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A302" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B302" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C302" s="7"/>
+      <c r="D302" s="7">
+        <v>298</v>
+      </c>
+      <c r="E302" s="4">
+        <v>11.384300000000001</v>
+      </c>
+      <c r="F302" s="7">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A303" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B303" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C303" s="7"/>
+      <c r="D303" s="7">
+        <v>64</v>
+      </c>
+      <c r="E303" s="4">
+        <v>11.790399999999996</v>
+      </c>
+      <c r="F303" s="7">
+        <v>41.4</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A304" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B304" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C304" s="7"/>
+      <c r="D304" s="7">
+        <v>293</v>
+      </c>
+      <c r="E304" s="4">
+        <v>12.125425000000002</v>
+      </c>
+      <c r="F304" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A305" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B305" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C305" s="7"/>
+      <c r="D305" s="7">
+        <v>235</v>
+      </c>
+      <c r="E305" s="4">
+        <v>10.856999999999999</v>
+      </c>
+      <c r="F305" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A306" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B306" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C306" s="7"/>
+      <c r="D306" s="7">
+        <v>289</v>
+      </c>
+      <c r="E306" s="4">
+        <v>11.272324999999999</v>
+      </c>
+      <c r="F306" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A307" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B307" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C307" s="7"/>
+      <c r="D307" s="7">
+        <v>147</v>
+      </c>
+      <c r="E307" s="4">
+        <v>11.799899999999997</v>
+      </c>
+      <c r="F307" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A308" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B308" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C308" s="7"/>
+      <c r="D308" s="7">
+        <v>301</v>
+      </c>
+      <c r="E308" s="4">
+        <v>15.201074999999999</v>
+      </c>
+      <c r="F308" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A309" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B309" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C309" s="7"/>
+      <c r="D309" s="7">
+        <v>217</v>
+      </c>
+      <c r="E309" s="4">
+        <v>12.524000000000001</v>
+      </c>
+      <c r="F309" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A310" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B310" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C310" s="7"/>
+      <c r="D310" s="7">
+        <v>128</v>
+      </c>
+      <c r="E310" s="4">
+        <v>11.436699999999998</v>
+      </c>
+      <c r="F310" s="7">
+        <v>41.5</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A311" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B311" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C311" s="7"/>
+      <c r="D311" s="7">
+        <v>294</v>
+      </c>
+      <c r="E311" s="4">
+        <v>12.630550000000001</v>
+      </c>
+      <c r="F311" s="7">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A312" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B312" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C312" s="7"/>
+      <c r="D312" s="7">
+        <v>297</v>
+      </c>
+      <c r="E312" s="4">
+        <v>12.4285</v>
+      </c>
+      <c r="F312" s="7">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A313" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B313" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7">
+        <v>276</v>
+      </c>
+      <c r="E313" s="4">
+        <v>12.147874999999999</v>
+      </c>
+      <c r="F313" s="7">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="314" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A314" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B314" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C314" s="7"/>
+      <c r="D314" s="7">
+        <v>262</v>
+      </c>
+      <c r="E314" s="4">
+        <v>13.472424999999998</v>
+      </c>
+      <c r="F314" s="7">
+        <v>41.6</v>
+      </c>
+    </row>
+    <row r="315" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A315" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B315" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C315" s="7"/>
+      <c r="D315" s="7">
+        <v>248</v>
+      </c>
+      <c r="E315" s="4">
+        <v>11.519274999999997</v>
+      </c>
+      <c r="F315" s="7">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="316" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A316" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B316" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C316" s="7"/>
+      <c r="D316" s="7">
+        <v>234</v>
+      </c>
+      <c r="E316" s="4">
+        <v>13.225474999999996</v>
+      </c>
+      <c r="F316" s="7">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="317" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A317" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B317" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C317" s="7"/>
+      <c r="D317" s="7">
+        <v>78</v>
+      </c>
+      <c r="E317" s="4">
+        <v>12.989750000000001</v>
+      </c>
+      <c r="F317" s="7">
+        <v>41.7</v>
+      </c>
+    </row>
+    <row r="318" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A318" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B318" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C318" s="7"/>
+      <c r="D318" s="7">
+        <v>295</v>
+      </c>
+      <c r="E318" s="4">
+        <v>13.315274999999998</v>
+      </c>
+      <c r="F318" s="7">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="319" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A319" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B319" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C319" s="7"/>
+      <c r="D319" s="7">
+        <v>296</v>
+      </c>
+      <c r="E319" s="4">
+        <v>11.957050000000001</v>
+      </c>
+      <c r="F319" s="7">
+        <v>41.8</v>
+      </c>
+    </row>
+    <row r="320" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A320" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B320" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C320" s="7"/>
+      <c r="D320" s="7">
+        <v>249</v>
+      </c>
+      <c r="E320" s="4">
+        <v>12.944849999999995</v>
+      </c>
+      <c r="F320" s="7">
+        <v>41.9</v>
+      </c>
+    </row>
+    <row r="321" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A321" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B321" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C321" s="7"/>
+      <c r="D321" s="7">
+        <v>277</v>
+      </c>
+      <c r="E321" s="4">
+        <v>12.551974999999995</v>
+      </c>
+      <c r="F321" s="7">
+        <v>42.1</v>
+      </c>
+    </row>
+    <row r="322" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A322" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B322" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C322" s="7"/>
+      <c r="D322" s="7">
+        <v>311</v>
+      </c>
+      <c r="E322" s="4">
+        <v>13.135675000000001</v>
+      </c>
+      <c r="F322" s="7">
+        <v>42.2</v>
+      </c>
+    </row>
+    <row r="323" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A323" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B323" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C323" s="7"/>
+      <c r="D323" s="7">
+        <v>110</v>
+      </c>
+      <c r="E323" s="4">
+        <v>12.922399999999998</v>
+      </c>
+      <c r="F323" s="7">
+        <v>42.3</v>
+      </c>
+    </row>
+    <row r="324" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A324" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B324" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C324" s="7"/>
+      <c r="D324" s="7">
+        <v>263</v>
+      </c>
+      <c r="E324" s="4">
+        <v>12.31625</v>
+      </c>
+      <c r="F324" s="7">
+        <v>42.4</v>
+      </c>
+    </row>
+    <row r="325" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A325" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="B325" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C325" s="7"/>
+      <c r="D325" s="7">
+        <v>290</v>
+      </c>
+      <c r="E325" s="4">
+        <v>12.507074999999999</v>
+      </c>
+      <c r="F325" s="7">
+        <v>42.4</v>
+      </c>
     </row>
     <row r="3685" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C3685" s="3"/>
@@ -24561,20 +29160,7 @@
       <c r="K8635" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="G123:G133"/>
-    <mergeCell ref="G79:G89"/>
-    <mergeCell ref="G57:G67"/>
-    <mergeCell ref="G112:G122"/>
-    <mergeCell ref="G13:G23"/>
-    <mergeCell ref="G2:G12"/>
-    <mergeCell ref="G35:G45"/>
-    <mergeCell ref="G46:G56"/>
-    <mergeCell ref="G68:G78"/>
-    <mergeCell ref="G90:G100"/>
-    <mergeCell ref="G24:G34"/>
-    <mergeCell ref="G101:G111"/>
-  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddHeader>&amp;R&amp;"Calibri"&amp;1 &amp;K000000 Interní / Internal#_x000D_</oddHeader>
@@ -24592,13 +29178,13 @@
         <v>2</v>
       </c>
       <c r="B1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" t="s">
         <v>17</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>18</v>
-      </c>
-      <c r="D1" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.3">
